--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7716-2024</t>
+          <t>A 31291-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45349</v>
+        <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1346,261 +1346,261 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Sandödla
+Hasselmus</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7716-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Ängskovall</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 951-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45301</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>28.1</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bredbrämad bastardsvärmare
 Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31291-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Sandödla
-Hasselmus</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46114</v>
+        <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1786,38 +1786,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46114</v>
+        <v>45318</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,17 +1847,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1880,49 +1880,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46125</v>
+        <v>45407</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1996,38 +1996,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45343</v>
+        <v>46114</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2056,16 +2056,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>22.7</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2074,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2086,58 +2081,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45434</v>
+        <v>46114</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,7 +2162,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2200,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2211,38 +2206,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45600</v>
+        <v>46125</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,7 +2267,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2316,38 +2311,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46183</v>
+        <v>44844</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,7 +2372,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2417,42 +2412,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2461,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44844</v>
+        <v>45343</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2481,8 +2476,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>22.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2518,46 +2518,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2567,14 +2567,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46258</v>
+        <v>46183</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,19 +2587,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2614,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2627,46 +2627,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2676,14 +2672,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>46258</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2695,13 +2691,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2710,10 +2701,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2728,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2741,42 +2732,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2790,10 +2785,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45407</v>
+        <v>45434</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2806,7 +2801,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2850,38 +2845,38 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2895,10 +2890,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45318</v>
+        <v>45069</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2910,20 +2905,25 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>11.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2938,7 +2938,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2947,39 +2947,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45329</v>
+        <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,13 +3371,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3415,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,10 +3429,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45755</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3449,8 +3444,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45324</v>
+        <v>45318</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,13 +3522,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3571,7 +3566,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45555</v>
+        <v>44827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3644,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3658,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45330</v>
+        <v>45180</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3673,13 +3668,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>18.4</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3739,7 +3729,7 @@
         <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3795,7 +3785,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3809,10 +3799,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45498</v>
+        <v>45324</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3830,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3873,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3887,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45089</v>
+        <v>45162</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3903,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3946,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3960,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45343</v>
+        <v>45652</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3976,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4019,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4033,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44657</v>
+        <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4048,13 +4038,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4097,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4111,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45426</v>
+        <v>45336</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4126,13 +4111,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4175,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4185,14 +4165,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45700</v>
+        <v>45397</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4205,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4248,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4262,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44923</v>
+        <v>46035</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4278,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4321,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4331,14 +4311,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45875</v>
+        <v>45700</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4351,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4394,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4408,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45273</v>
+        <v>45875</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4424,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4464,7 @@
         <v>45818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4540,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4554,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45740</v>
+        <v>45600</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4570,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4613,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4627,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45971</v>
+        <v>45273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4643,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4686,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4700,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45043</v>
+        <v>44845</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4716,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>14</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4759,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4773,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45317</v>
+        <v>45769</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4789,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4832,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4846,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45993</v>
+        <v>45343</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4861,13 +4841,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4910,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4924,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45547</v>
+        <v>45971</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4940,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4983,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4997,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45429</v>
+        <v>44943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5013,7 +4988,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5056,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5070,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45112</v>
+        <v>45180</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5085,13 +5060,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5134,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5148,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45392</v>
+        <v>45993</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5163,8 +5133,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5207,7 +5182,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5221,10 +5196,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45392</v>
+        <v>45343</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5236,8 +5211,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5280,7 +5260,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5294,10 +5274,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45838</v>
+        <v>45112</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5309,8 +5289,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5353,7 +5338,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5367,10 +5352,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45336</v>
+        <v>45838</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5383,7 +5368,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5426,7 +5411,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5440,10 +5425,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45318</v>
+        <v>45320</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5456,7 +5441,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5499,7 +5484,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5513,10 +5498,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45318</v>
+        <v>45547</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5529,7 +5514,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5572,7 +5557,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5586,10 +5571,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45348</v>
+        <v>45875</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5602,7 +5587,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5645,7 +5630,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5659,10 +5644,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45532</v>
+        <v>46006</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5675,7 +5660,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5718,7 +5703,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5732,10 +5717,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45318</v>
+        <v>45317</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5791,7 +5776,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5805,10 +5790,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46035</v>
+        <v>46125</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5821,7 +5806,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5864,7 +5849,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5878,10 +5863,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45162</v>
+        <v>45392</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5894,7 +5879,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5937,7 +5922,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5951,10 +5936,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45180</v>
+        <v>45392</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5967,7 +5952,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6010,7 +5995,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6024,10 +6009,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45061</v>
+        <v>45318</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6040,7 +6025,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6083,7 +6068,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6097,10 +6082,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45569</v>
+        <v>45318</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6113,7 +6098,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6156,7 +6141,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6170,10 +6155,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45334</v>
+        <v>46266</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6186,7 +6171,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6229,7 +6214,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6243,10 +6228,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45162</v>
+        <v>45061</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6259,7 +6244,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6302,7 +6287,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6316,10 +6301,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45092</v>
+        <v>44876</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6332,7 +6317,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6375,7 +6360,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6389,10 +6374,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45628</v>
+        <v>45555</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6405,7 +6390,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7.5</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6448,7 +6433,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6462,10 +6447,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45755</v>
+        <v>45429</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6478,7 +6463,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6521,7 +6506,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6535,10 +6520,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46006</v>
+        <v>45498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6550,8 +6535,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6594,7 +6584,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6608,10 +6598,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45875</v>
+        <v>44903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6624,7 +6614,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6667,7 +6657,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6681,10 +6671,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44720</v>
+        <v>45569</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6697,7 +6687,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6740,7 +6730,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6754,10 +6744,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45318</v>
+        <v>45392</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6770,7 +6760,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6813,7 +6803,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6827,10 +6817,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45399</v>
+        <v>44657</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6842,8 +6832,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6886,7 +6881,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6900,10 +6895,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45397</v>
+        <v>45348</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6916,7 +6911,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6959,7 +6954,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6973,10 +6968,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45162</v>
+        <v>45043</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6989,7 +6984,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7032,7 +7027,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7046,10 +7041,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45343</v>
+        <v>45318</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7061,13 +7056,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>10.6</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7110,7 +7100,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7124,10 +7114,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45320</v>
+        <v>45162</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7140,7 +7130,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7183,7 +7173,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7197,10 +7187,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45652</v>
+        <v>44720</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7213,7 +7203,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7256,7 +7246,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7270,10 +7260,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46125</v>
+        <v>45755</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7286,7 +7276,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7329,7 +7319,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7343,10 +7333,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45318</v>
+        <v>45532</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7359,7 +7349,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7402,7 +7392,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7412,14 +7402,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45628</v>
+        <v>45320</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7432,7 +7422,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7475,7 +7465,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7489,10 +7479,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44903</v>
+        <v>44923</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7505,7 +7495,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7548,7 +7538,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7562,10 +7552,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44922</v>
+        <v>45434</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7577,13 +7567,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7626,7 +7611,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7640,10 +7625,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44876</v>
+        <v>45334</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7656,7 +7641,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7699,7 +7684,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7713,10 +7698,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45434</v>
+        <v>45329</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7728,8 +7713,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7772,7 +7762,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7786,10 +7776,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45320</v>
+        <v>45330</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7801,8 +7791,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>18.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7840,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7854,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44943</v>
+        <v>45089</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7875,7 +7870,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7913,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7927,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45572</v>
+        <v>45426</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7947,8 +7942,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44827</v>
+        <v>45399</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44845</v>
+        <v>45755</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>14</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45180</v>
+        <v>45092</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45769</v>
+        <v>45318</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45392</v>
+        <v>45162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8366,14 +8366,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46266</v>
+        <v>45628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8443,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45600</v>
+        <v>45628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8519,7 +8519,7 @@
         <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31291-2026</t>
+          <t>A 7716-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46218</v>
+        <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1346,261 +1346,261 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Ängskovall</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 951-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare
+Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31291-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sandödla
 Hasselmus</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 7716-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Ängskovall</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 951-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Bredbrämad bastardsvärmare
-Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45600</v>
+        <v>46114</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1786,38 +1786,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45318</v>
+        <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,16 +1847,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1880,49 +1880,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45407</v>
+        <v>46125</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1996,38 +1996,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46114</v>
+        <v>44844</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,20 +2057,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2081,58 +2081,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46114</v>
+        <v>46183</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,20 +2162,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2186,58 +2186,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46125</v>
+        <v>45343</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2266,21 +2266,26 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>22.7</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2291,10 +2296,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2303,46 +2308,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44844</v>
+        <v>45434</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2384,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2396,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2412,42 +2417,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2461,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45343</v>
+        <v>45600</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2476,16 +2481,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>22.7</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2518,46 +2518,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2567,14 +2567,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46183</v>
+        <v>46258</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,19 +2587,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2614,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2627,42 +2627,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2672,14 +2676,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46258</v>
+        <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2691,8 +2695,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2701,10 +2710,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2719,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2732,46 +2741,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2785,10 +2790,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45434</v>
+        <v>45407</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2801,7 +2806,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2845,38 +2850,38 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2890,10 +2895,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45069</v>
+        <v>45318</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2905,25 +2910,20 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>11.4</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2938,7 +2938,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2947,39 +2947,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45572</v>
+        <v>44720</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3415,7 +3415,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>45875</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3444,13 +3444,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3488,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3502,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45318</v>
+        <v>45755</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3523,7 +3518,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3566,7 +3561,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3580,10 +3575,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44827</v>
+        <v>45329</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3595,8 +3590,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3639,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45180</v>
+        <v>45318</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3712,7 +3712,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44978</v>
+        <v>45399</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
         <v>45324</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45162</v>
+        <v>45397</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45652</v>
+        <v>45330</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3965,8 +3965,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>18.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4014,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4028,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45740</v>
+        <v>45555</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4044,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4087,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4101,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45336</v>
+        <v>45162</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4117,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4160,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4174,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45397</v>
+        <v>44978</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4190,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4233,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4247,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46035</v>
+        <v>45498</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4257,8 +4262,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4311,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4311,14 +4321,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45700</v>
+        <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4341,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4384,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4398,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45875</v>
+        <v>45343</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4403,8 +4413,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>10.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4462,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4461,10 +4476,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45818</v>
+        <v>45320</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4492,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.7</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4535,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4549,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45600</v>
+        <v>45652</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4593,7 +4608,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4622,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45273</v>
+        <v>45318</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4638,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4681,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4676,14 +4691,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44845</v>
+        <v>45628</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4711,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>14</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4754,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4768,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45769</v>
+        <v>44903</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4784,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4827,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4841,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45343</v>
+        <v>44922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4841,8 +4856,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4905,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4919,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45971</v>
+        <v>45343</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4935,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4978,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4992,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44943</v>
+        <v>45112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4987,8 +5007,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5056,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5070,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45180</v>
+        <v>45838</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5086,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5129,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5143,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45993</v>
+        <v>45818</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5133,13 +5158,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5182,7 +5202,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5196,10 +5216,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45343</v>
+        <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5217,7 +5237,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10.6</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5260,7 +5280,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5274,10 +5294,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45112</v>
+        <v>45426</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5295,7 +5315,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5338,7 +5358,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5352,10 +5372,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45838</v>
+        <v>44923</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5368,7 +5388,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5411,7 +5431,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5425,10 +5445,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45320</v>
+        <v>45971</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5441,7 +5461,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5484,7 +5504,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5498,10 +5518,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45547</v>
+        <v>45273</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5514,7 +5534,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5557,7 +5577,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5571,10 +5591,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45875</v>
+        <v>45993</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5586,8 +5606,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>7.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5630,7 +5655,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5644,10 +5669,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46006</v>
+        <v>45740</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5660,7 +5685,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5703,7 +5728,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5717,10 +5742,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45317</v>
+        <v>45043</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5733,7 +5758,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5776,7 +5801,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5790,10 +5815,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46125</v>
+        <v>45317</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5806,7 +5831,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5849,7 +5874,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5863,10 +5888,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45392</v>
+        <v>46006</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5879,7 +5904,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5922,7 +5947,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5936,10 +5961,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45392</v>
+        <v>45875</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5952,7 +5977,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5995,7 +6020,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6009,10 +6034,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45318</v>
+        <v>44876</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6068,7 +6093,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6082,10 +6107,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45318</v>
+        <v>45434</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6098,7 +6123,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6141,7 +6166,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6155,10 +6180,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46266</v>
+        <v>45320</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6171,7 +6196,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6214,7 +6239,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6228,10 +6253,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45061</v>
+        <v>44943</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6244,7 +6269,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6</v>
+        <v>0.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6287,7 +6312,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6301,10 +6326,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44876</v>
+        <v>45572</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6317,7 +6342,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6360,7 +6385,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6374,10 +6399,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45555</v>
+        <v>45547</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6390,7 +6415,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6450,7 +6475,7 @@
         <v>45429</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6506,7 +6531,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6520,10 +6545,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45498</v>
+        <v>45392</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6535,13 +6560,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6584,7 +6604,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6598,10 +6618,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44903</v>
+        <v>45392</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6614,7 +6634,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6657,7 +6677,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6671,10 +6691,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45569</v>
+        <v>46035</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6687,7 +6707,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6730,7 +6750,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6744,10 +6764,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45392</v>
+        <v>45336</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6760,7 +6780,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6803,7 +6823,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6817,10 +6837,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44657</v>
+        <v>45318</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6832,13 +6852,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6881,7 +6896,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6895,10 +6910,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45348</v>
+        <v>45318</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6911,7 +6926,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.9</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6954,7 +6969,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6968,10 +6983,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45043</v>
+        <v>44827</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6984,7 +6999,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7027,7 +7042,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7041,10 +7056,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45318</v>
+        <v>44845</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7057,7 +7072,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>14</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7100,7 +7115,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7114,10 +7129,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45162</v>
+        <v>46125</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7130,7 +7145,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7173,7 +7188,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7187,10 +7202,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44720</v>
+        <v>45348</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7203,7 +7218,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>6.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7246,7 +7261,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7260,10 +7275,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45755</v>
+        <v>45532</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7276,7 +7291,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7319,7 +7334,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7333,10 +7348,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45532</v>
+        <v>45318</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7349,7 +7364,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7392,7 +7407,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7406,10 +7421,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45320</v>
+        <v>45162</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7422,7 +7437,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7465,7 +7480,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7479,10 +7494,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44923</v>
+        <v>45180</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7495,7 +7510,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7538,7 +7553,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7552,10 +7567,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45434</v>
+        <v>45180</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7568,7 +7583,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7611,7 +7626,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7625,10 +7640,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45334</v>
+        <v>45061</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7641,7 +7656,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7684,7 +7699,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7698,10 +7713,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45329</v>
+        <v>45569</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7713,13 +7728,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7762,7 +7772,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7776,10 +7786,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45330</v>
+        <v>45334</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7791,13 +7801,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>18.4</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7840,7 +7845,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7854,10 +7859,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45089</v>
+        <v>45162</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7870,7 +7875,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7913,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7927,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45426</v>
+        <v>45769</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7942,13 +7947,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45399</v>
+        <v>45092</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45755</v>
+        <v>45628</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>7.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45092</v>
+        <v>45755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45318</v>
+        <v>45392</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45162</v>
+        <v>46266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8366,14 +8366,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45628</v>
+        <v>45600</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8443,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45628</v>
+        <v>45204</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8458,8 +8458,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8502,7 +8507,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8516,10 +8521,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45204</v>
+        <v>45728</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8537,7 +8542,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8580,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8590,14 +8595,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45728</v>
+        <v>45700</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8609,13 +8614,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 951-2024</t>
+          <t>A 31291-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45301</v>
+        <v>46218</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1419,16 +1419,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>28.1</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1458,149 +1453,154 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Sandödla
+Hasselmus</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 951-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bredbrämad bastardsvärmare
 Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31291-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Sandödla
-Hasselmus</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46114</v>
+        <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1786,38 +1786,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46114</v>
+        <v>45318</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,17 +1847,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1880,49 +1880,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46125</v>
+        <v>45407</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1996,31 +1996,31 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
         <v>44844</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46183</v>
+        <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2161,8 +2161,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>22.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2198,46 +2203,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2256,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45343</v>
+        <v>46114</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2266,16 +2271,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>22.7</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2296,58 +2296,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45434</v>
+        <v>46114</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2410,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2421,38 +2421,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45600</v>
+        <v>46125</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2526,38 +2526,38 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2567,14 +2567,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46258</v>
+        <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2627,39 +2627,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
@@ -2683,7 +2679,7 @@
         <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2776,7 +2772,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2790,10 +2786,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45407</v>
+        <v>46183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2806,20 +2802,20 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -2830,10 +2826,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2846,42 +2842,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2891,14 +2887,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45318</v>
+        <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2911,10 +2907,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2947,39 +2943,43 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44720</v>
+        <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3415,7 +3415,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45875</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3444,8 +3444,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3488,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3502,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45755</v>
+        <v>45318</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3518,7 +3523,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3561,7 +3566,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3575,10 +3580,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45329</v>
+        <v>44827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3590,13 +3595,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3639,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45318</v>
+        <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3666,6 +3666,11 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -3712,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3726,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45399</v>
+        <v>45162</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3742,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3785,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3799,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45324</v>
+        <v>45180</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3814,13 +3819,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45397</v>
+        <v>44978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45330</v>
+        <v>45652</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3965,13 +3965,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4014,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4028,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45555</v>
+        <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4044,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4087,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4101,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45162</v>
+        <v>45336</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4117,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4160,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4174,10 +4169,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44978</v>
+        <v>45397</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4190,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4233,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4247,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45498</v>
+        <v>45600</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4262,13 +4257,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4311,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4325,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45089</v>
+        <v>45273</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4341,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4384,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4398,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45343</v>
+        <v>44845</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4413,13 +4403,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>10.6</v>
+        <v>14</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4462,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4472,14 +4457,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45320</v>
+        <v>45700</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4492,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4535,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4549,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45652</v>
+        <v>45875</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4565,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4608,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4622,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45318</v>
+        <v>45769</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4638,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4681,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4691,14 +4676,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45628</v>
+        <v>45818</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4711,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4754,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4768,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44903</v>
+        <v>46035</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4784,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4827,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4841,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44922</v>
+        <v>45343</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4856,13 +4841,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4905,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4919,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45343</v>
+        <v>45971</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4935,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4978,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4992,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45112</v>
+        <v>44943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5007,13 +4987,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5056,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5070,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45838</v>
+        <v>45180</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5086,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5129,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5143,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45818</v>
+        <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5158,8 +5133,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>6.7</v>
+        <v>10.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5202,7 +5182,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5216,10 +5196,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44657</v>
+        <v>45993</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5237,7 +5217,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5280,7 +5260,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5294,10 +5274,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45426</v>
+        <v>45320</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5309,13 +5289,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5358,7 +5333,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5372,10 +5347,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44923</v>
+        <v>45547</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5388,7 +5363,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5431,7 +5406,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5445,10 +5420,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45971</v>
+        <v>45317</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5461,7 +5436,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5504,7 +5479,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5518,10 +5493,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45273</v>
+        <v>45392</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5534,7 +5509,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5577,7 +5552,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5591,10 +5566,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45993</v>
+        <v>45392</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5606,13 +5581,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>7.8</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5655,7 +5625,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5669,10 +5639,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45740</v>
+        <v>45112</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5684,8 +5654,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5728,7 +5703,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5742,10 +5717,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45043</v>
+        <v>45318</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5758,7 +5733,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5801,7 +5776,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5815,10 +5790,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45317</v>
+        <v>45318</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5831,7 +5806,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5874,7 +5849,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5888,10 +5863,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46006</v>
+        <v>45838</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5904,7 +5879,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5947,7 +5922,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5961,10 +5936,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45875</v>
+        <v>45061</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5977,7 +5952,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6037,7 +6012,7 @@
         <v>44876</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6093,7 +6068,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6107,10 +6082,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45434</v>
+        <v>45555</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6166,7 +6141,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6180,10 +6155,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45320</v>
+        <v>45429</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6196,7 +6171,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6239,7 +6214,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6253,10 +6228,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44943</v>
+        <v>45498</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6268,8 +6243,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6312,7 +6292,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6326,10 +6306,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45572</v>
+        <v>44903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6342,7 +6322,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6385,7 +6365,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6399,10 +6379,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45547</v>
+        <v>45569</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6415,7 +6395,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6458,7 +6438,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6472,10 +6452,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45429</v>
+        <v>45392</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6488,7 +6468,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6531,7 +6511,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6545,10 +6525,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45392</v>
+        <v>44657</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6560,8 +6540,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6604,7 +6589,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6618,10 +6603,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45392</v>
+        <v>45875</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6634,7 +6619,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6677,7 +6662,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6691,10 +6676,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46035</v>
+        <v>46006</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6707,7 +6692,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6750,7 +6735,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6764,10 +6749,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45336</v>
+        <v>45348</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6780,7 +6765,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6823,7 +6808,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6837,10 +6822,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45318</v>
+        <v>45043</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6853,7 +6838,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6896,7 +6881,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6913,7 +6898,7 @@
         <v>45318</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6926,7 +6911,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6969,7 +6954,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6983,10 +6968,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44827</v>
+        <v>45162</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6999,7 +6984,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7042,7 +7027,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7056,10 +7041,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44845</v>
+        <v>46125</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7072,7 +7057,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>14</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7115,7 +7100,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7129,10 +7114,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46125</v>
+        <v>44720</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7145,7 +7130,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7188,7 +7173,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7202,10 +7187,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45348</v>
+        <v>45755</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7218,7 +7203,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.9</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7278,7 +7263,7 @@
         <v>45532</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7334,7 +7319,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7348,10 +7333,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45318</v>
+        <v>45320</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7364,7 +7349,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7407,7 +7392,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7421,10 +7406,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45162</v>
+        <v>44923</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7437,7 +7422,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7480,7 +7465,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7494,10 +7479,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45180</v>
+        <v>45434</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7510,7 +7495,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7553,7 +7538,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7567,10 +7552,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45180</v>
+        <v>45334</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7583,7 +7568,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7626,7 +7611,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7640,10 +7625,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45061</v>
+        <v>45329</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7655,8 +7640,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7699,7 +7689,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7713,10 +7703,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45569</v>
+        <v>45330</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7728,8 +7718,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>18.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7772,7 +7767,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7786,10 +7781,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45334</v>
+        <v>45089</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7802,7 +7797,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7840,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7854,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45162</v>
+        <v>45426</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7874,8 +7869,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45769</v>
+        <v>45399</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45092</v>
+        <v>46266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45628</v>
+        <v>45755</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.5</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45755</v>
+        <v>45092</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45392</v>
+        <v>45318</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46266</v>
+        <v>45162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8366,14 +8366,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45600</v>
+        <v>45628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8443,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45204</v>
+        <v>45628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8458,13 +8458,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8507,7 +8502,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8521,10 +8516,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45728</v>
+        <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8542,7 +8537,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8585,7 +8580,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8595,14 +8590,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45700</v>
+        <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8614,8 +8609,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7716-2024</t>
+          <t>A 31291-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45349</v>
+        <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1346,150 +1346,150 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Sandödla
+Hasselmus</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7716-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Ängskovall</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 31291-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Sandödla
-Hasselmus</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45600</v>
+        <v>46114</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1786,38 +1786,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45318</v>
+        <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,16 +1847,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1880,49 +1880,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45407</v>
+        <v>46125</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1996,38 +1996,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44844</v>
+        <v>45343</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2056,8 +2056,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>22.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2093,46 +2098,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45343</v>
+        <v>45434</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2161,16 +2166,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>22.7</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2191,10 +2191,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2203,46 +2203,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46114</v>
+        <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,20 +2272,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2296,58 +2296,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46114</v>
+        <v>45600</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2410,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2421,38 +2421,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2462,14 +2462,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46125</v>
+        <v>46258</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2491,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2522,42 +2522,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2571,10 +2575,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45434</v>
+        <v>44844</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,20 +2591,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2611,10 +2615,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2627,35 +2631,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
@@ -2679,7 +2683,7 @@
         <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2772,7 +2776,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2786,10 +2790,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46183</v>
+        <v>45407</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2802,10 +2806,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2814,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2826,10 +2830,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2842,42 +2846,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2887,14 +2891,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46258</v>
+        <v>45318</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2907,10 +2911,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2943,43 +2947,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45572</v>
+        <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,8 +3371,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3415,7 +3420,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3429,10 +3434,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>45755</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3444,13 +3449,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45318</v>
+        <v>45324</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,8 +3522,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3566,7 +3571,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44827</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3595,8 +3600,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>18.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3639,7 +3649,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,10 +3663,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45324</v>
+        <v>45555</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3668,13 +3678,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3722,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3736,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45162</v>
+        <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3752,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3795,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3809,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45180</v>
+        <v>45498</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3819,8 +3824,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3873,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3887,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44978</v>
+        <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3903,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3946,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3960,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45652</v>
+        <v>45343</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3976,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4019,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4033,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45740</v>
+        <v>44657</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4038,8 +4048,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4097,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4111,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45336</v>
+        <v>45426</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4111,8 +4126,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4175,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4165,14 +4185,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45397</v>
+        <v>45700</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4205,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4248,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4262,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45600</v>
+        <v>44923</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4278,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4321,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4335,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45273</v>
+        <v>45875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4351,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4394,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4408,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44845</v>
+        <v>45273</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4424,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>14</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4467,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4457,14 +4477,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45700</v>
+        <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4476,8 +4496,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4545,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4559,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45875</v>
+        <v>45838</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4575,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4618,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4632,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45769</v>
+        <v>45740</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4648,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4691,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4705,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45818</v>
+        <v>45043</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4721,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.7</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4764,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4778,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46035</v>
+        <v>45317</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4794,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4837,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4851,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45343</v>
+        <v>45547</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4867,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4910,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4924,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45971</v>
+        <v>45429</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4940,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4983,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4997,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44943</v>
+        <v>45392</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4988,7 +5013,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.1</v>
+        <v>5.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5056,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5070,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45180</v>
+        <v>45392</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5086,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5129,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5143,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45343</v>
+        <v>45336</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5133,13 +5158,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5182,7 +5202,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5196,10 +5216,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45993</v>
+        <v>45318</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5211,13 +5231,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5260,7 +5275,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5274,10 +5289,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45320</v>
+        <v>45318</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5290,7 +5305,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5333,7 +5348,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5347,10 +5362,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45547</v>
+        <v>46006</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5363,7 +5378,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5406,7 +5421,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5420,10 +5435,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45317</v>
+        <v>45875</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5436,7 +5451,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5479,7 +5494,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5493,10 +5508,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45392</v>
+        <v>45348</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5509,7 +5524,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5552,7 +5567,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5566,10 +5581,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45392</v>
+        <v>45532</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5582,7 +5597,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5625,7 +5640,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5639,10 +5654,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45112</v>
+        <v>45318</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5654,13 +5669,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5703,7 +5713,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5717,10 +5727,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45318</v>
+        <v>45818</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5733,7 +5743,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>6.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5776,7 +5786,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5790,10 +5800,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45318</v>
+        <v>45162</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5806,7 +5816,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5849,7 +5859,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5863,10 +5873,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45838</v>
+        <v>45180</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5879,7 +5889,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5939,7 +5949,7 @@
         <v>45061</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5995,7 +6005,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6009,10 +6019,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44876</v>
+        <v>45569</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6068,7 +6078,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6082,10 +6092,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45555</v>
+        <v>45334</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6098,7 +6108,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6141,7 +6151,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6155,10 +6165,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45429</v>
+        <v>46125</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6171,7 +6181,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6214,7 +6224,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6228,10 +6238,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45498</v>
+        <v>45162</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6243,13 +6253,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6292,7 +6297,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6306,10 +6311,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44903</v>
+        <v>45971</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6322,7 +6327,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6365,7 +6370,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6379,10 +6384,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45569</v>
+        <v>45092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6395,7 +6400,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6438,7 +6443,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6452,10 +6457,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45392</v>
+        <v>45628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6468,7 +6473,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>7.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6511,7 +6516,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6525,10 +6530,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44657</v>
+        <v>45755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6540,13 +6545,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6589,7 +6589,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45875</v>
+        <v>44720</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46006</v>
+        <v>45993</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6691,8 +6691,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6735,7 +6740,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6749,10 +6754,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45348</v>
+        <v>45318</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6765,7 +6770,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6808,7 +6813,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6822,10 +6827,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45043</v>
+        <v>45399</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6838,7 +6843,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6881,7 +6886,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6895,10 +6900,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45318</v>
+        <v>45397</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6911,7 +6916,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6954,7 +6959,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6968,10 +6973,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45162</v>
+        <v>46266</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6984,7 +6989,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7027,7 +7032,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7041,10 +7046,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46125</v>
+        <v>45162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7057,7 +7062,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7100,7 +7105,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7114,10 +7119,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44720</v>
+        <v>45343</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7129,8 +7134,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>10.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7173,7 +7183,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7187,10 +7197,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45755</v>
+        <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7246,7 +7256,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7260,10 +7270,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45532</v>
+        <v>45652</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7276,7 +7286,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7319,7 +7329,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7333,10 +7343,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45320</v>
+        <v>45318</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7349,7 +7359,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7392,7 +7402,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7402,14 +7412,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44923</v>
+        <v>45628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7422,7 +7432,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7465,7 +7475,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7479,10 +7489,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45434</v>
+        <v>44903</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7495,7 +7505,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7538,7 +7548,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7552,10 +7562,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45334</v>
+        <v>44922</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7567,8 +7577,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7611,7 +7626,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7625,10 +7640,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45329</v>
+        <v>44876</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7640,13 +7655,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7689,7 +7699,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7703,10 +7713,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45330</v>
+        <v>45434</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7718,13 +7728,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>18.4</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7767,7 +7772,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7781,10 +7786,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45089</v>
+        <v>45320</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7797,7 +7802,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7840,7 +7845,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7854,10 +7859,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45426</v>
+        <v>44943</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7869,13 +7874,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45399</v>
+        <v>45572</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46266</v>
+        <v>44827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45755</v>
+        <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>14</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45092</v>
+        <v>46035</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45318</v>
+        <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45162</v>
+        <v>45769</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8366,14 +8366,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45628</v>
+        <v>45392</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8443,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45628</v>
+        <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8519,7 +8519,7 @@
         <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31291-2026</t>
+          <t>A 7716-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46218</v>
+        <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1346,261 +1346,261 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Ängskovall</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 951-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare
+Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31291-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sandödla
 Hasselmus</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 7716-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Ängskovall</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 951-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Bredbrämad bastardsvärmare
-Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46114</v>
+        <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1786,38 +1786,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46114</v>
+        <v>45407</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1891,38 +1891,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46125</v>
+        <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,20 +1952,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1992,35 +1992,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
         <v>45343</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45434</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45600</v>
+        <v>45069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2376,8 +2376,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>11.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2389,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2401,10 +2406,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2417,42 +2422,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2462,14 +2467,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46258</v>
+        <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2487,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2491,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2506,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2515,53 +2520,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2575,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44844</v>
+        <v>46114</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2591,10 +2592,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2603,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2615,58 +2616,58 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2680,10 +2681,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>46125</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2695,13 +2696,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>11.4</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2713,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2725,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2741,42 +2737,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2786,14 +2782,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45407</v>
+        <v>46258</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2806,7 +2802,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2815,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2830,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2846,35 +2842,39 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>45318</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45329</v>
+        <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,13 +3371,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3415,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,10 +3429,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45755</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3449,8 +3444,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45324</v>
+        <v>45318</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,13 +3522,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3571,7 +3566,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>44827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3600,13 +3595,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>18.4</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3649,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3663,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45555</v>
+        <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3678,8 +3668,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3722,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3736,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44978</v>
+        <v>45162</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3752,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3795,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3809,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45498</v>
+        <v>45652</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3824,13 +3819,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3873,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3887,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45089</v>
+        <v>45740</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3903,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3946,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3960,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45343</v>
+        <v>45180</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3976,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4019,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4033,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44657</v>
+        <v>44978</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4048,13 +4038,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4097,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4111,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45426</v>
+        <v>45336</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4126,13 +4111,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4175,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4185,14 +4165,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45700</v>
+        <v>45397</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4205,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4248,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4262,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44923</v>
+        <v>45273</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4278,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4321,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4335,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45875</v>
+        <v>44845</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4351,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>14</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4394,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4408,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45273</v>
+        <v>45600</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4424,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4467,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4481,10 +4461,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45112</v>
+        <v>45769</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4496,13 +4476,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4545,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4559,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45838</v>
+        <v>45343</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4575,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4618,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4632,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45740</v>
+        <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4648,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4691,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4705,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45043</v>
+        <v>45180</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4721,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4764,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4778,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45317</v>
+        <v>45343</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,8 +4768,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>10.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4837,7 +4817,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4851,10 +4831,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45547</v>
+        <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,8 +4846,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4910,7 +4895,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4924,10 +4909,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45429</v>
+        <v>45838</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4940,7 +4925,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4983,7 +4968,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4997,10 +4982,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45392</v>
+        <v>45320</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5013,7 +4998,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5056,7 +5041,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5070,10 +5055,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45392</v>
+        <v>45547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5086,7 +5071,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5129,7 +5114,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5143,10 +5128,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45336</v>
+        <v>45317</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5159,7 +5144,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5202,7 +5187,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5216,10 +5201,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45318</v>
+        <v>45818</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5232,7 +5217,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>6.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5275,7 +5260,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5289,10 +5274,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45318</v>
+        <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5305,7 +5290,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5348,7 +5333,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5362,10 +5347,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46006</v>
+        <v>45392</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5378,7 +5363,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5421,7 +5406,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5435,10 +5420,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45875</v>
+        <v>45971</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5451,7 +5436,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5494,7 +5479,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5508,10 +5493,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45348</v>
+        <v>45318</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5524,7 +5509,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.9</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5567,7 +5552,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5581,10 +5566,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45532</v>
+        <v>45318</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5597,7 +5582,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5640,7 +5625,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5654,10 +5639,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45318</v>
+        <v>45061</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5670,7 +5655,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5713,7 +5698,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5727,10 +5712,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45818</v>
+        <v>44876</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5743,7 +5728,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.7</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5786,7 +5771,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5800,10 +5785,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45162</v>
+        <v>45555</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5816,7 +5801,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5859,7 +5844,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5873,10 +5858,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45180</v>
+        <v>45993</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5888,8 +5873,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5932,7 +5922,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5946,10 +5936,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45061</v>
+        <v>45429</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5962,7 +5952,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6005,7 +5995,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6019,10 +6009,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45569</v>
+        <v>45498</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6034,8 +6024,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6078,7 +6073,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6092,10 +6087,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45334</v>
+        <v>45875</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6108,7 +6103,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6151,7 +6146,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6165,10 +6160,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46125</v>
+        <v>46006</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6181,7 +6176,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6224,7 +6219,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6238,10 +6233,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45162</v>
+        <v>44903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6254,7 +6249,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6297,7 +6292,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6311,10 +6306,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45971</v>
+        <v>45569</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6327,7 +6322,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6370,7 +6365,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6384,10 +6379,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45092</v>
+        <v>45392</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6443,7 +6438,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6457,10 +6452,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45628</v>
+        <v>44657</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6472,8 +6467,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45755</v>
+        <v>45348</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6589,7 +6589,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44720</v>
+        <v>45043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45993</v>
+        <v>46035</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6691,13 +6691,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6757,7 +6752,7 @@
         <v>45318</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6813,7 +6808,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6827,10 +6822,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45399</v>
+        <v>45162</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6843,7 +6838,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6886,7 +6881,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6900,10 +6895,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45397</v>
+        <v>46125</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6916,7 +6911,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6959,7 +6954,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6973,10 +6968,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46266</v>
+        <v>44720</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6989,7 +6984,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7032,7 +7027,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7046,10 +7041,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45162</v>
+        <v>45755</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7062,7 +7057,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7105,7 +7100,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7119,10 +7114,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45343</v>
+        <v>45532</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7134,13 +7129,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7183,7 +7173,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7200,7 +7190,7 @@
         <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7213,7 +7203,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7256,7 +7246,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7270,10 +7260,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45652</v>
+        <v>44923</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7286,7 +7276,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7329,7 +7319,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7343,10 +7333,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45318</v>
+        <v>45434</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7359,7 +7349,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7402,7 +7392,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7412,14 +7402,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45628</v>
+        <v>45334</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7432,7 +7422,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7475,7 +7465,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7489,10 +7479,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44903</v>
+        <v>45329</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7504,8 +7494,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7548,7 +7543,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7562,10 +7557,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44922</v>
+        <v>45330</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7583,7 +7578,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>18.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7626,7 +7621,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7640,10 +7635,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44876</v>
+        <v>45089</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7656,7 +7651,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7699,7 +7694,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7713,10 +7708,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45434</v>
+        <v>45426</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7728,8 +7723,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7772,7 +7772,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7786,10 +7786,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45320</v>
+        <v>45399</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44943</v>
+        <v>45755</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45572</v>
+        <v>45092</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44827</v>
+        <v>45318</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44845</v>
+        <v>45162</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8147,14 +8147,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46035</v>
+        <v>45628</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45180</v>
+        <v>45628</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45769</v>
+        <v>46266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45392</v>
+        <v>45204</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8385,8 +8385,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8434,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8448,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45600</v>
+        <v>45728</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8458,8 +8463,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8502,7 +8512,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8512,14 +8522,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45204</v>
+        <v>45700</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8531,13 +8541,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8580,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8594,10 +8599,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45728</v>
+        <v>45875</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8609,13 +8614,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45301</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46218</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45407</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45343</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45434</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>46114</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>46125</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>46258</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45318</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45318</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>44827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45162</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45652</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45740</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>45180</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44978</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45336</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45397</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45273</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>44845</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45600</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45769</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45343</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45180</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45343</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45838</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>45320</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>45547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>45317</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45818</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45392</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45971</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>45318</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>45318</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45061</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>44876</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45555</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45993</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>45429</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>45498</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45875</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>46006</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>45569</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45392</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44657</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45348</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>45043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>46035</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>45318</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>45162</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>46125</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44720</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>45755</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45532</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44923</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45434</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>45334</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>45329</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45330</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>45089</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>45426</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>45399</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45755</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>45092</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45318</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>45162</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>45628</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>45628</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>46266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>45204</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45728</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>45700</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45875</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 951-2024</t>
+          <t>A 31291-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45301</v>
+        <v>46218</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1419,16 +1419,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>28.1</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1458,149 +1453,154 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Sandödla
+Hasselmus</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 951-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bredbrämad bastardsvärmare
 Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31291-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Sandödla
-Hasselmus</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45407</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45343</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45434</v>
+        <v>46183</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,20 +2167,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2191,10 +2191,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46183</v>
+        <v>45434</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2296,10 +2296,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2312,42 +2312,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45069</v>
+        <v>46114</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2376,13 +2376,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>11.4</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2394,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2406,58 +2401,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2474,7 +2469,7 @@
         <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2487,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2520,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2531,38 +2526,38 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2576,10 +2571,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2592,7 +2587,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2625,7 +2620,7 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2636,38 +2631,38 @@
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2681,10 +2676,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46125</v>
+        <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,8 +2691,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>11.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2737,35 +2737,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
         <v>46258</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45318</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45572</v>
+        <v>44922</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,8 +3371,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3415,7 +3420,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3429,10 +3434,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>45572</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3444,13 +3449,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>45318</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>44827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45162</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45652</v>
+        <v>45180</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45740</v>
+        <v>44978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45180</v>
+        <v>45652</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44978</v>
+        <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>45336</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45397</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45273</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>44845</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45600</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45769</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45343</v>
+        <v>45875</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44943</v>
+        <v>45343</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45180</v>
+        <v>45112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4695,8 +4695,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4744,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4758,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45343</v>
+        <v>45838</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4768,13 +4773,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>10.6</v>
+        <v>4.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45112</v>
+        <v>44943</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4846,13 +4846,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4895,7 +4890,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4909,10 +4904,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45838</v>
+        <v>45180</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4925,7 +4920,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4968,7 +4963,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4982,10 +4977,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45320</v>
+        <v>45343</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4997,8 +4992,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>10.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5041,7 +5041,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45547</v>
+        <v>45818</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5114,7 +5114,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45317</v>
+        <v>45320</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5187,7 +5187,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45818</v>
+        <v>45971</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45392</v>
+        <v>45547</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5347,10 +5347,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45392</v>
+        <v>45875</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45971</v>
+        <v>46006</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5479,7 +5479,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45318</v>
+        <v>45317</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45318</v>
+        <v>45993</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5581,8 +5581,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5625,7 +5630,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5639,10 +5644,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45061</v>
+        <v>45392</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5655,7 +5660,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5698,7 +5703,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5712,10 +5717,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44876</v>
+        <v>45392</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5728,7 +5733,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5771,7 +5776,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5785,10 +5790,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45555</v>
+        <v>45318</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5801,7 +5806,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5844,7 +5849,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5858,10 +5863,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45993</v>
+        <v>45318</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5873,13 +5878,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>7.8</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45429</v>
+        <v>45061</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6009,10 +6009,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45498</v>
+        <v>44876</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6024,13 +6024,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6073,7 +6068,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6087,10 +6082,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45875</v>
+        <v>45555</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6103,7 +6098,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6146,7 +6141,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6160,10 +6155,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46006</v>
+        <v>46125</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6176,7 +6171,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6219,7 +6214,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6233,10 +6228,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44903</v>
+        <v>45429</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6249,7 +6244,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6292,7 +6287,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6306,10 +6301,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45569</v>
+        <v>46035</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6322,7 +6317,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6365,7 +6360,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6379,10 +6374,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45392</v>
+        <v>45498</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6394,8 +6389,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6452,10 +6452,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44657</v>
+        <v>44903</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6467,13 +6467,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6516,7 +6511,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6530,10 +6525,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45348</v>
+        <v>45569</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6546,7 +6541,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.9</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6589,7 +6584,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6603,10 +6598,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45043</v>
+        <v>45392</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6619,7 +6614,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6662,7 +6657,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6676,10 +6671,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46035</v>
+        <v>44657</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6691,8 +6686,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6735,7 +6735,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45318</v>
+        <v>45348</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6808,7 +6808,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45162</v>
+        <v>45043</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46125</v>
+        <v>45318</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44720</v>
+        <v>45162</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7027,7 +7027,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45755</v>
+        <v>44720</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7100,7 +7100,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7114,10 +7114,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45532</v>
+        <v>45755</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7173,7 +7173,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45320</v>
+        <v>45532</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7246,7 +7246,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7260,10 +7260,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44923</v>
+        <v>45320</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7319,7 +7319,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7333,10 +7333,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45434</v>
+        <v>44923</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7392,7 +7392,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45334</v>
+        <v>45434</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7465,7 +7465,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45329</v>
+        <v>46266</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7494,13 +7494,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7543,7 +7538,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7557,10 +7552,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45330</v>
+        <v>45334</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7572,13 +7567,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>18.4</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7621,7 +7611,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7635,10 +7625,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45089</v>
+        <v>45329</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7650,8 +7640,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7694,7 +7689,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7708,10 +7703,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45426</v>
+        <v>45330</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7729,7 +7724,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>18.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7772,7 +7767,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7786,10 +7781,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45399</v>
+        <v>45089</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7802,7 +7797,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7840,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7854,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45755</v>
+        <v>45426</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7874,8 +7869,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45092</v>
+        <v>45399</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45318</v>
+        <v>45755</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45162</v>
+        <v>45092</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>9</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8147,14 +8147,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45628</v>
+        <v>45318</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45628</v>
+        <v>45162</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8293,14 +8293,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46266</v>
+        <v>45628</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45204</v>
+        <v>45628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8385,13 +8385,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8434,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8448,10 +8443,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45728</v>
+        <v>45204</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8469,7 +8464,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8512,7 +8507,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8522,14 +8517,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45700</v>
+        <v>45728</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8541,8 +8536,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8595,14 +8595,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45875</v>
+        <v>45700</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 31291-2026</t>
+          <t>A 951-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46218</v>
+        <v>45301</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1419,11 +1419,16 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>28.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1453,154 +1458,149 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare
+Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31291-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sandödla
 Hasselmus</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 951-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Bredbrämad bastardsvärmare
-Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45600</v>
+        <v>45343</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1741,21 +1741,26 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>22.7</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -1766,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1778,46 +1783,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1836,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45407</v>
+        <v>45434</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,7 +1852,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1891,38 +1896,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44844</v>
+        <v>45600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,10 +1957,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1964,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1976,10 +1981,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1992,42 +1997,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45343</v>
+        <v>45318</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2056,13 +2061,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>22.7</v>
+        <v>6.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2071,10 +2071,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2102,42 +2102,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46183</v>
+        <v>44844</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45434</v>
+        <v>46114</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2305,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2316,38 +2316,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2364,7 +2364,7 @@
         <v>46114</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2410,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2421,38 +2421,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2515,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2526,38 +2526,38 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46125</v>
+        <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2586,8 +2586,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>11.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2599,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2611,10 +2616,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2627,42 +2632,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2676,10 +2681,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>45407</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2691,13 +2696,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>11.4</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2737,42 +2737,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2782,14 +2782,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46258</v>
+        <v>46183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2842,46 +2842,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2891,14 +2887,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45318</v>
+        <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2911,10 +2907,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2947,39 +2943,43 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25822-2022</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44733</v>
+        <v>45273</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44922</v>
+        <v>45204</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 25822-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45572</v>
+        <v>44733</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45318</v>
+        <v>45329</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,8 +3522,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3566,7 +3571,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44827</v>
+        <v>45728</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3595,8 +3600,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3639,7 +3649,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,10 +3663,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45324</v>
+        <v>45740</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3668,13 +3678,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3722,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3736,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45162</v>
+        <v>45043</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3752,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3795,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3809,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45180</v>
+        <v>45317</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3863,7 +3868,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3882,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44978</v>
+        <v>45755</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3898,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3941,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3955,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45652</v>
+        <v>45547</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4009,7 +4014,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4028,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45740</v>
+        <v>45429</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4044,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4087,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4101,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45336</v>
+        <v>45392</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4117,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4160,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4174,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45397</v>
+        <v>45392</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4190,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4233,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4247,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45273</v>
+        <v>45324</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4257,8 +4262,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4311,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4325,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44845</v>
+        <v>45336</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4341,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>14</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4384,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4398,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45600</v>
+        <v>45318</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4414,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4457,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4461,10 +4471,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45769</v>
+        <v>45318</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4487,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4530,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4544,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45875</v>
+        <v>45330</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4549,8 +4559,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>18.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4608,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4622,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45343</v>
+        <v>45555</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4638,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4681,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4695,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45112</v>
+        <v>45348</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4695,13 +4710,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4744,7 +4754,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4758,10 +4768,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45838</v>
+        <v>44978</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4774,7 +4784,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4817,7 +4827,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4831,10 +4841,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44943</v>
+        <v>45532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4847,7 +4857,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4890,7 +4900,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4904,10 +4914,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45180</v>
+        <v>45498</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4919,8 +4929,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4963,7 +4978,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4977,10 +4992,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45343</v>
+        <v>45318</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4992,13 +5007,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>10.6</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5041,7 +5051,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5055,10 +5065,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45818</v>
+        <v>45089</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5071,7 +5081,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5114,7 +5124,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5128,10 +5138,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45320</v>
+        <v>45162</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5144,7 +5154,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5187,7 +5197,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5201,10 +5211,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45971</v>
+        <v>45180</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5217,7 +5227,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5260,7 +5270,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5274,10 +5284,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45547</v>
+        <v>45061</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5290,7 +5300,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5333,7 +5343,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5347,10 +5357,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45875</v>
+        <v>45569</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5363,7 +5373,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5406,7 +5416,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5420,10 +5430,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46006</v>
+        <v>45334</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5436,7 +5446,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5479,7 +5489,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5493,10 +5503,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45317</v>
+        <v>45818</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5509,7 +5519,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5552,7 +5562,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5566,10 +5576,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45993</v>
+        <v>45343</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5581,13 +5591,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5630,7 +5635,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5644,10 +5649,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45392</v>
+        <v>45162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5660,7 +5665,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5703,7 +5708,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5717,10 +5722,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45392</v>
+        <v>45092</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5733,7 +5738,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5776,7 +5781,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5790,10 +5795,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45318</v>
+        <v>45628</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5806,7 +5811,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5849,7 +5854,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5863,10 +5868,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45318</v>
+        <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5878,8 +5883,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5922,7 +5932,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5936,10 +5946,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45061</v>
+        <v>45755</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5952,7 +5962,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5995,7 +6005,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6009,10 +6019,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44876</v>
+        <v>45426</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6024,8 +6034,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6068,7 +6083,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6082,10 +6097,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45555</v>
+        <v>45971</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6098,7 +6113,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6141,7 +6156,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6155,10 +6170,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46125</v>
+        <v>44923</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6171,7 +6186,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6214,7 +6229,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6228,10 +6243,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45429</v>
+        <v>44720</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6244,7 +6259,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6287,7 +6302,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6301,10 +6316,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46035</v>
+        <v>45993</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6316,8 +6331,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>7.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6360,7 +6380,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6374,10 +6394,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45498</v>
+        <v>45318</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6389,13 +6409,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6438,7 +6453,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6452,10 +6467,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44903</v>
+        <v>45399</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6468,7 +6483,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6511,7 +6526,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6525,10 +6540,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45569</v>
+        <v>45397</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6541,7 +6556,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6584,7 +6599,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6598,10 +6613,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45392</v>
+        <v>45162</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6614,7 +6629,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6657,7 +6672,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6671,10 +6686,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44657</v>
+        <v>45343</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6692,7 +6707,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.4</v>
+        <v>10.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6735,7 +6750,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6749,10 +6764,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45348</v>
+        <v>45320</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6765,7 +6780,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.9</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6808,7 +6823,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6822,10 +6837,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45043</v>
+        <v>46035</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6838,7 +6853,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6881,7 +6896,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6895,10 +6910,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45318</v>
+        <v>45652</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6911,7 +6926,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6954,7 +6969,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6968,10 +6983,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45162</v>
+        <v>45318</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6984,7 +6999,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7027,7 +7042,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7037,14 +7052,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44720</v>
+        <v>45628</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7057,7 +7072,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7100,7 +7115,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7114,10 +7129,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45755</v>
+        <v>44903</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7130,7 +7145,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7173,7 +7188,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7187,10 +7202,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45532</v>
+        <v>44922</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7202,8 +7217,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7246,7 +7266,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7260,10 +7280,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45320</v>
+        <v>46266</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7276,7 +7296,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7319,7 +7339,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7333,10 +7353,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44923</v>
+        <v>44876</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7349,7 +7369,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7409,7 +7429,7 @@
         <v>45434</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7465,7 +7485,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7479,10 +7499,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46266</v>
+        <v>45320</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7495,7 +7515,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7538,7 +7558,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7548,14 +7568,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45334</v>
+        <v>45700</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7568,7 +7588,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7611,7 +7631,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7625,10 +7645,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45329</v>
+        <v>44943</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7640,13 +7660,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7689,7 +7704,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7703,10 +7718,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45330</v>
+        <v>45572</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7718,13 +7733,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>18.4</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7767,7 +7777,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7781,10 +7791,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45089</v>
+        <v>44827</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7797,7 +7807,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7840,7 +7850,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7854,10 +7864,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45426</v>
+        <v>44845</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7869,13 +7879,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>14</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7923,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7937,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45399</v>
+        <v>45875</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7953,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7996,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8010,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45755</v>
+        <v>45180</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8026,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8069,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8083,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45092</v>
+        <v>45112</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8093,8 +8098,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8147,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8161,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45318</v>
+        <v>45838</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8177,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8220,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8234,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45162</v>
+        <v>45769</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8250,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8293,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8293,14 +8303,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45628</v>
+        <v>45392</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8323,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8366,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8370,10 +8380,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45628</v>
+        <v>45600</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8396,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8439,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8453,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45204</v>
+        <v>46006</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8458,13 +8468,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8507,7 +8512,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8521,10 +8526,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45728</v>
+        <v>45875</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8536,13 +8541,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8595,14 +8595,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45700</v>
+        <v>46125</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 951-2024</t>
+          <t>A 31291-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45301</v>
+        <v>46218</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1419,16 +1419,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>28.1</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1458,149 +1453,154 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Sandödla
+Hasselmus</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 951-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bredbrämad bastardsvärmare
 Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31291-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Sandödla
-Hasselmus</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45343</v>
+        <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1741,16 +1741,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>22.7</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1759,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1771,10 +1766,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1783,46 +1778,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1836,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45434</v>
+        <v>45407</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1852,7 +1847,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1896,38 +1891,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45600</v>
+        <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1957,20 +1952,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1981,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1997,42 +1992,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45318</v>
+        <v>45343</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2061,8 +2056,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>6.8</v>
+        <v>22.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2071,10 +2071,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2102,42 +2102,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44844</v>
+        <v>45434</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2191,10 +2191,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46114</v>
+        <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,20 +2272,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2296,58 +2296,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2364,7 +2364,7 @@
         <v>46114</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2410,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2421,38 +2421,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46125</v>
+        <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2515,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2526,38 +2526,38 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45069</v>
+        <v>46125</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2586,13 +2586,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>11.4</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2604,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2616,10 +2611,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2632,42 +2627,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2681,10 +2676,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45407</v>
+        <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,8 +2691,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>11.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2737,42 +2737,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2782,14 +2782,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46183</v>
+        <v>46258</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2842,42 +2842,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2887,14 +2891,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46258</v>
+        <v>45318</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2907,10 +2911,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2943,43 +2947,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 25822-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45273</v>
+        <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45204</v>
+        <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,13 +3371,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3415,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25822-2022</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,10 +3429,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44733</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3449,8 +3444,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45329</v>
+        <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,13 +3522,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3571,7 +3566,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45728</v>
+        <v>45318</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3600,13 +3595,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3649,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3663,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45740</v>
+        <v>45180</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3722,7 +3712,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3736,10 +3726,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45043</v>
+        <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3752,7 +3742,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3795,7 +3785,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3809,10 +3799,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45317</v>
+        <v>45324</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3824,8 +3814,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3868,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3882,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45755</v>
+        <v>45162</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3898,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3941,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3955,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45547</v>
+        <v>45652</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4014,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4028,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45429</v>
+        <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4044,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4087,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4101,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45392</v>
+        <v>45336</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4117,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4160,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4174,10 +4169,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45392</v>
+        <v>45397</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4190,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4233,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4247,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45324</v>
+        <v>45600</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4262,13 +4257,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4311,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4325,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45336</v>
+        <v>45273</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4341,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4384,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4398,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45318</v>
+        <v>44845</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4414,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>14</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4457,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4471,10 +4461,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45318</v>
+        <v>45769</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4487,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4530,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4544,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45330</v>
+        <v>45875</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4559,13 +4549,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>18.4</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4608,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4622,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45555</v>
+        <v>45343</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4638,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4681,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4695,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45348</v>
+        <v>44943</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4711,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.9</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4754,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4768,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44978</v>
+        <v>45180</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4784,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4827,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4841,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45532</v>
+        <v>45343</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4856,8 +4841,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4900,7 +4890,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4914,10 +4904,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45498</v>
+        <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4935,7 +4925,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4978,7 +4968,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4992,10 +4982,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45318</v>
+        <v>45838</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5008,7 +4998,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5051,7 +5041,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5065,10 +5055,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45089</v>
+        <v>45818</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5081,7 +5071,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5124,7 +5114,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5138,10 +5128,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45162</v>
+        <v>45320</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5154,7 +5144,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5197,7 +5187,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5211,10 +5201,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45180</v>
+        <v>45547</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5227,7 +5217,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5270,7 +5260,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5284,10 +5274,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45061</v>
+        <v>45971</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5300,7 +5290,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5343,7 +5333,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5357,10 +5347,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45569</v>
+        <v>45317</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5373,7 +5363,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5416,7 +5406,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5430,10 +5420,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45334</v>
+        <v>45993</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5445,8 +5435,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5489,7 +5484,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5503,10 +5498,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45818</v>
+        <v>45392</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5519,7 +5514,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5562,7 +5557,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5576,10 +5571,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45343</v>
+        <v>45392</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5592,7 +5587,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5635,7 +5630,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5649,10 +5644,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45162</v>
+        <v>45318</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5665,7 +5660,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5708,7 +5703,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5722,10 +5717,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45092</v>
+        <v>45318</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5738,7 +5733,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5781,7 +5776,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5795,10 +5790,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45628</v>
+        <v>45061</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5811,7 +5806,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5854,7 +5849,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5868,10 +5863,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44657</v>
+        <v>44876</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5883,13 +5878,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5932,7 +5922,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5946,10 +5936,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45755</v>
+        <v>45555</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5962,7 +5952,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6005,7 +5995,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6019,10 +6009,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45426</v>
+        <v>45429</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6034,13 +6024,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6083,7 +6068,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6097,10 +6082,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45971</v>
+        <v>45875</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6113,7 +6098,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6156,7 +6141,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6170,10 +6155,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44923</v>
+        <v>46006</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6186,7 +6171,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6229,7 +6214,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6243,10 +6228,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44720</v>
+        <v>45498</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6258,8 +6243,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6302,7 +6292,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6316,10 +6306,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45993</v>
+        <v>46035</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6331,13 +6321,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6380,7 +6365,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6394,10 +6379,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45318</v>
+        <v>44903</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6410,7 +6395,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6453,7 +6438,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6467,10 +6452,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45399</v>
+        <v>45569</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6483,7 +6468,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6526,7 +6511,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6540,10 +6525,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45397</v>
+        <v>45392</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6556,7 +6541,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6599,7 +6584,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6613,10 +6598,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45162</v>
+        <v>44657</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6628,8 +6613,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6672,7 +6662,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6686,10 +6676,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45343</v>
+        <v>45348</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6701,13 +6691,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>10.6</v>
+        <v>6.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6750,7 +6735,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6764,10 +6749,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45320</v>
+        <v>45043</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6780,7 +6765,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6823,7 +6808,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6837,10 +6822,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46035</v>
+        <v>46125</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6853,7 +6838,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6896,7 +6881,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6910,10 +6895,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45652</v>
+        <v>45318</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6926,7 +6911,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6969,7 +6954,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6983,10 +6968,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45318</v>
+        <v>45162</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6999,7 +6984,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7042,7 +7027,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7052,14 +7037,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45628</v>
+        <v>44720</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7072,7 +7057,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7115,7 +7100,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7129,10 +7114,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44903</v>
+        <v>45755</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7145,7 +7130,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7188,7 +7173,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7202,10 +7187,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44922</v>
+        <v>45532</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7217,13 +7202,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7266,7 +7246,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7280,10 +7260,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46266</v>
+        <v>45320</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7296,7 +7276,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7339,7 +7319,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7353,10 +7333,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44876</v>
+        <v>44923</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7369,7 +7349,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7429,7 +7409,7 @@
         <v>45434</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7485,7 +7465,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7499,10 +7479,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45320</v>
+        <v>45334</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7515,7 +7495,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7558,7 +7538,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7568,14 +7548,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45700</v>
+        <v>45329</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7587,8 +7567,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7631,7 +7616,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7645,10 +7630,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44943</v>
+        <v>45330</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7660,8 +7645,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.1</v>
+        <v>18.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7704,7 +7694,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7718,10 +7708,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45572</v>
+        <v>45089</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7734,7 +7724,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7777,7 +7767,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7791,10 +7781,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44827</v>
+        <v>45426</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7806,8 +7796,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7850,7 +7845,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7864,10 +7859,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44845</v>
+        <v>45399</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7880,7 +7875,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>14</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7923,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7937,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45875</v>
+        <v>45755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7953,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7996,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8010,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45180</v>
+        <v>45092</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8026,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8069,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8083,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45112</v>
+        <v>45318</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8098,13 +8093,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8147,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8161,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45838</v>
+        <v>45162</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8177,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8220,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8230,14 +8220,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45769</v>
+        <v>45628</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8250,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8293,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8307,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45392</v>
+        <v>45628</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8323,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>7.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8366,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8380,10 +8370,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45600</v>
+        <v>45204</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8393,6 +8383,11 @@
       <c r="G96" t="inlineStr">
         <is>
           <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -8439,7 +8434,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8453,10 +8448,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46006</v>
+        <v>45728</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8468,8 +8463,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8512,7 +8512,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45875</v>
+        <v>46266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8595,14 +8595,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46125</v>
+        <v>45700</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7716-2024</t>
+          <t>A 31291-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45349</v>
+        <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1346,150 +1346,150 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Sandödla
+Hasselmus</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7716-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Ängskovall</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 31291-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Sandödla
-Hasselmus</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45600</v>
+        <v>46114</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1786,38 +1786,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45407</v>
+        <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1891,38 +1891,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44844</v>
+        <v>46125</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45343</v>
+        <v>45318</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2056,13 +2056,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>22.7</v>
+        <v>6.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2071,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2089,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2102,42 +2097,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45434</v>
+        <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2166,21 +2161,26 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>22.7</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2191,10 +2191,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2203,39 +2203,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46114</v>
+        <v>45434</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2410,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2421,38 +2421,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46114</v>
+        <v>45600</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2515,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2526,38 +2526,38 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2567,14 +2567,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46125</v>
+        <v>46258</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2627,42 +2627,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2676,10 +2680,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>44844</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2691,16 +2695,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>11.4</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2737,42 +2736,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2782,14 +2781,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46258</v>
+        <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2801,8 +2800,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2811,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2829,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2842,46 +2846,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45318</v>
+        <v>45407</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2911,16 +2911,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2947,39 +2947,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45572</v>
+        <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,8 +3371,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3415,7 +3420,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3429,10 +3434,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>45755</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3444,13 +3449,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44827</v>
+        <v>45324</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,8 +3522,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3566,7 +3571,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45318</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3595,8 +3600,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>18.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3639,7 +3649,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,10 +3663,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45180</v>
+        <v>45555</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3669,7 +3679,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3729,7 +3739,7 @@
         <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3785,7 +3795,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3799,10 +3809,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45324</v>
+        <v>45498</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3830,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3873,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3887,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45162</v>
+        <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3903,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3946,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3960,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45652</v>
+        <v>46035</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3976,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4019,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4033,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45740</v>
+        <v>45343</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4049,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4092,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4106,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45336</v>
+        <v>45818</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4122,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>6.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4165,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4179,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45397</v>
+        <v>44657</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4184,8 +4194,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4243,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4257,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45600</v>
+        <v>45426</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4257,8 +4272,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4321,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4335,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45273</v>
+        <v>44923</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4351,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4394,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4408,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44845</v>
+        <v>45971</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4424,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4467,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4461,10 +4481,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45769</v>
+        <v>45273</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4497,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4540,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4554,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45875</v>
+        <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4549,8 +4569,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4618,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4632,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45343</v>
+        <v>45838</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4648,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4691,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4705,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44943</v>
+        <v>45993</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4695,8 +4720,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.1</v>
+        <v>7.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4769,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4783,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45180</v>
+        <v>45740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4799,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4842,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4856,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45343</v>
+        <v>45043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4841,13 +4871,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>10.6</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4890,7 +4915,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4904,10 +4929,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45112</v>
+        <v>45317</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4919,13 +4944,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4968,7 +4988,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4982,10 +5002,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45838</v>
+        <v>45547</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4998,7 +5018,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5041,7 +5061,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5055,10 +5075,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45818</v>
+        <v>45429</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5071,7 +5091,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.7</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5114,7 +5134,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5128,10 +5148,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45320</v>
+        <v>45392</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5144,7 +5164,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5187,7 +5207,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5201,10 +5221,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45547</v>
+        <v>45392</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5217,7 +5237,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5260,7 +5280,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5274,10 +5294,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45971</v>
+        <v>45336</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5290,7 +5310,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5333,7 +5353,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5347,10 +5367,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45317</v>
+        <v>46006</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5363,7 +5383,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5406,7 +5426,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5420,10 +5440,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45993</v>
+        <v>45875</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5435,13 +5455,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>7.8</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5484,7 +5499,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5498,10 +5513,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45392</v>
+        <v>45318</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5514,7 +5529,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5557,7 +5572,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5571,10 +5586,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45392</v>
+        <v>45318</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5587,7 +5602,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5630,7 +5645,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5640,14 +5655,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45318</v>
+        <v>45700</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5703,7 +5718,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5717,10 +5732,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45318</v>
+        <v>45348</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5733,7 +5748,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.4</v>
+        <v>6.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5776,7 +5791,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5790,10 +5805,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45061</v>
+        <v>45532</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5806,7 +5821,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5849,7 +5864,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5863,10 +5878,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44876</v>
+        <v>45318</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5879,7 +5894,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5922,7 +5937,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5936,10 +5951,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45555</v>
+        <v>45162</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5952,7 +5967,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5995,7 +6010,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6009,10 +6024,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45429</v>
+        <v>45180</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6025,7 +6040,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6068,7 +6083,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6085,7 +6100,7 @@
         <v>45875</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6098,7 +6113,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6141,7 +6156,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6155,10 +6170,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46006</v>
+        <v>46125</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6171,7 +6186,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6214,7 +6229,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6228,10 +6243,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45498</v>
+        <v>45061</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6243,13 +6258,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6292,7 +6302,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6306,10 +6316,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46035</v>
+        <v>45569</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6322,7 +6332,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6365,7 +6375,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6379,10 +6389,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44903</v>
+        <v>45334</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6395,7 +6405,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6438,7 +6448,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6452,10 +6462,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45569</v>
+        <v>45162</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6468,7 +6478,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6511,7 +6521,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6525,10 +6535,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45392</v>
+        <v>45092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6584,7 +6594,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6598,10 +6608,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44657</v>
+        <v>45628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6613,13 +6623,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6662,7 +6667,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6676,10 +6681,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45348</v>
+        <v>45755</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6692,7 +6697,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.9</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6735,7 +6740,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6749,10 +6754,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45043</v>
+        <v>44720</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6765,7 +6770,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6808,7 +6813,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6822,10 +6827,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46125</v>
+        <v>45318</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6838,7 +6843,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6881,7 +6886,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6895,10 +6900,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45318</v>
+        <v>45399</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6911,7 +6916,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6954,7 +6959,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6968,10 +6973,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45162</v>
+        <v>45397</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6984,7 +6989,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7027,7 +7032,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7041,10 +7046,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44720</v>
+        <v>45162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7057,7 +7062,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7100,7 +7105,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7114,10 +7119,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45755</v>
+        <v>45343</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7129,8 +7134,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>10.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7173,7 +7183,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7187,10 +7197,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45532</v>
+        <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7203,7 +7213,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7246,7 +7256,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7260,10 +7270,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45320</v>
+        <v>45652</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7276,7 +7286,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7319,7 +7329,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7333,10 +7343,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44923</v>
+        <v>45318</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7349,7 +7359,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7392,7 +7402,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7402,14 +7412,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45434</v>
+        <v>45628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7422,7 +7432,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7465,7 +7475,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7479,10 +7489,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45334</v>
+        <v>44903</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7495,7 +7505,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7538,7 +7548,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7552,10 +7562,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45329</v>
+        <v>44922</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7573,7 +7583,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7616,7 +7626,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7630,10 +7640,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45330</v>
+        <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7645,13 +7655,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>18.4</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7694,7 +7699,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7708,10 +7713,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45089</v>
+        <v>44876</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7724,7 +7729,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7767,7 +7772,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7781,10 +7786,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45426</v>
+        <v>45434</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7796,13 +7801,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45399</v>
+        <v>45320</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45755</v>
+        <v>44943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45092</v>
+        <v>45572</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45318</v>
+        <v>44827</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45162</v>
+        <v>44845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8220,14 +8220,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45628</v>
+        <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45628</v>
+        <v>45769</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.5</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45204</v>
+        <v>45392</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8385,13 +8385,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8434,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8448,10 +8443,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45728</v>
+        <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8463,13 +8458,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8512,7 +8502,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8526,10 +8516,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46266</v>
+        <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8541,8 +8531,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8585,7 +8580,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8595,14 +8590,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45700</v>
+        <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8614,8 +8609,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45349</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>46114</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46125</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45318</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45434</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45600</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>46258</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44844</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45407</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45755</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45324</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45555</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45498</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>46035</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>45343</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45818</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>44657</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45426</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44923</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45971</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45273</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>45838</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>45993</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>45740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>45043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45317</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>45547</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45429</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>45392</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45392</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45336</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>46006</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45875</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>45318</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>45318</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>45700</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>45348</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45532</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>45318</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>45162</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45180</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45875</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>46125</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45061</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>45569</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>45334</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45162</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>45092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>45628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45755</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44720</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>45318</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45399</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>45397</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>45162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>45343</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45652</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>45318</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>45628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>44903</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44922</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44876</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>45434</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45320</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45572</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44827</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>45769</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>45392</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45349</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>46114</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46125</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45318</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45434</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45600</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>46258</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44844</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45407</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45755</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45324</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45555</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45498</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>46035</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>45343</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45818</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>44657</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45426</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44923</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45971</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45273</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>45838</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>45993</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>45740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>45043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45317</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>45547</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45429</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>45392</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45392</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45336</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>46006</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45875</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>45318</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>45318</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>45700</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>45348</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45532</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>45318</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>45162</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45180</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45875</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>46125</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45061</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>45569</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>45334</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45162</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>45092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>45628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45755</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44720</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>45318</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45399</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>45397</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>45162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>45343</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45652</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>45318</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>45628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>44903</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44922</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44876</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>45434</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45320</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45572</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44827</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>45769</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>45392</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31291-2026</t>
+          <t>A 7716-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46218</v>
+        <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1346,150 +1346,150 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Ängskovall</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 31291-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Sandödla
 Hasselmus</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 7716-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Ängskovall</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
         <v/>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46114</v>
+        <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1786,38 +1786,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46114</v>
+        <v>45318</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,17 +1847,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1880,49 +1880,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46125</v>
+        <v>45407</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1996,38 +1996,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45318</v>
+        <v>44844</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2066,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2093,39 +2093,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46183</v>
+        <v>46114</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2296,58 +2296,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45434</v>
+        <v>46114</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2410,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2421,38 +2421,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45600</v>
+        <v>46125</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2526,38 +2526,38 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2567,14 +2567,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46258</v>
+        <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2627,46 +2627,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2680,10 +2676,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44844</v>
+        <v>46183</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2692,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2736,35 +2732,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
@@ -2788,7 +2784,7 @@
         <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2881,7 +2877,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2891,14 +2887,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45407</v>
+        <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2911,7 +2907,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2920,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2935,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2951,35 +2947,39 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45329</v>
+        <v>44922</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45755</v>
+        <v>45572</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45324</v>
+        <v>45318</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,13 +3522,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3571,7 +3566,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>44827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3600,13 +3595,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>18.4</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3649,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3663,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45555</v>
+        <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3678,8 +3668,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3722,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3736,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44978</v>
+        <v>45162</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3752,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3795,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3809,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45498</v>
+        <v>45728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3830,7 +3825,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3873,7 +3868,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3887,10 +3882,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45089</v>
+        <v>45180</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3903,7 +3898,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3946,7 +3941,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3960,10 +3955,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46035</v>
+        <v>44978</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3976,7 +3971,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4019,7 +4014,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4033,10 +4028,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45343</v>
+        <v>45652</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4049,7 +4044,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4092,7 +4087,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4106,10 +4101,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45818</v>
+        <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4122,7 +4117,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4165,7 +4160,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4179,10 +4174,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44657</v>
+        <v>45336</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4194,13 +4189,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4243,7 +4233,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4257,10 +4247,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45426</v>
+        <v>45397</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4272,13 +4262,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4321,7 +4306,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4335,10 +4320,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44923</v>
+        <v>45818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4351,7 +4336,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4394,7 +4379,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4404,14 +4389,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45971</v>
+        <v>45700</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4424,7 +4409,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4467,7 +4452,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4481,10 +4466,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45273</v>
+        <v>45875</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4497,7 +4482,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4540,7 +4525,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4554,10 +4539,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45112</v>
+        <v>45600</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4569,13 +4554,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4618,7 +4598,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4632,10 +4612,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45838</v>
+        <v>45273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4648,7 +4628,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4691,7 +4671,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4705,10 +4685,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45993</v>
+        <v>44845</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,13 +4700,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4769,7 +4744,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4783,10 +4758,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45740</v>
+        <v>45971</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4799,7 +4774,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4842,7 +4817,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4856,10 +4831,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45043</v>
+        <v>45769</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4872,7 +4847,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4915,7 +4890,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4929,10 +4904,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45317</v>
+        <v>45993</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4944,8 +4919,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4988,7 +4968,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5002,10 +4982,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45547</v>
+        <v>45343</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5018,7 +4998,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5061,7 +5041,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5075,10 +5055,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45429</v>
+        <v>46035</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5091,7 +5071,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5134,7 +5114,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5148,10 +5128,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45392</v>
+        <v>44943</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5164,7 +5144,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5207,7 +5187,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5221,10 +5201,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45392</v>
+        <v>45180</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5237,7 +5217,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5280,7 +5260,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5294,10 +5274,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45336</v>
+        <v>45343</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5309,8 +5289,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5353,7 +5338,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5367,10 +5352,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46006</v>
+        <v>45320</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5383,7 +5368,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5426,7 +5411,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5440,10 +5425,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45875</v>
+        <v>45547</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5456,7 +5441,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5499,7 +5484,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5513,10 +5498,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45318</v>
+        <v>45317</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5529,7 +5514,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5572,7 +5557,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5586,10 +5571,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45318</v>
+        <v>45392</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5602,7 +5587,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5645,7 +5630,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5655,14 +5640,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45700</v>
+        <v>45392</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5675,7 +5660,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5718,7 +5703,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5732,10 +5717,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45348</v>
+        <v>45112</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5747,8 +5732,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5791,7 +5781,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5805,10 +5795,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45532</v>
+        <v>45838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5821,7 +5811,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5864,7 +5854,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5881,7 +5871,7 @@
         <v>45318</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5894,7 +5884,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5937,7 +5927,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5951,10 +5941,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45162</v>
+        <v>45318</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5967,7 +5957,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6010,7 +6000,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6024,10 +6014,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45180</v>
+        <v>45061</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6040,7 +6030,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6083,7 +6073,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6097,10 +6087,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45875</v>
+        <v>44876</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6113,7 +6103,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6156,7 +6146,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6170,10 +6160,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46125</v>
+        <v>45555</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6186,7 +6176,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6229,7 +6219,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6243,10 +6233,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45061</v>
+        <v>45429</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6259,7 +6249,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6302,7 +6292,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6316,10 +6306,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45569</v>
+        <v>45498</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6331,8 +6321,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6375,7 +6370,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6389,10 +6384,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45334</v>
+        <v>44903</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6405,7 +6400,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6448,7 +6443,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6462,10 +6457,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45162</v>
+        <v>45569</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6478,7 +6473,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6521,7 +6516,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6535,10 +6530,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45092</v>
+        <v>45392</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6594,7 +6589,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6608,10 +6603,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45628</v>
+        <v>45875</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6624,7 +6619,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6667,7 +6662,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6681,10 +6676,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45755</v>
+        <v>46006</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6697,7 +6692,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6740,7 +6735,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6754,10 +6749,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44720</v>
+        <v>44657</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6769,8 +6764,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6813,7 +6813,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45318</v>
+        <v>45348</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6886,7 +6886,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6900,10 +6900,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45399</v>
+        <v>45043</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6959,7 +6959,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45397</v>
+        <v>45318</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7049,7 +7049,7 @@
         <v>45162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7105,7 +7105,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45343</v>
+        <v>46125</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7134,13 +7134,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>10.6</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7183,7 +7178,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7197,10 +7192,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45320</v>
+        <v>44720</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7213,7 +7208,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7256,7 +7251,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7270,10 +7265,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45652</v>
+        <v>45755</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7286,7 +7281,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7329,7 +7324,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7343,10 +7338,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45318</v>
+        <v>45532</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7359,7 +7354,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7402,7 +7397,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7412,14 +7407,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45628</v>
+        <v>45320</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7432,7 +7427,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7475,7 +7470,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7489,10 +7484,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44903</v>
+        <v>44923</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7505,7 +7500,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7548,7 +7543,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7562,10 +7557,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44922</v>
+        <v>45434</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7577,13 +7572,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7626,7 +7616,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7640,10 +7630,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46266</v>
+        <v>45334</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7656,7 +7646,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7699,7 +7689,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7713,10 +7703,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44876</v>
+        <v>45329</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7728,8 +7718,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7772,7 +7767,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7786,10 +7781,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45434</v>
+        <v>45330</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7801,8 +7796,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>18.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45320</v>
+        <v>45089</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44943</v>
+        <v>45426</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7947,8 +7947,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7996,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8010,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45572</v>
+        <v>45399</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8026,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8069,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8083,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44827</v>
+        <v>45755</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8099,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8142,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8156,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44845</v>
+        <v>45092</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8172,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>14</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8215,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8229,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45180</v>
+        <v>45318</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8245,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8288,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8302,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45769</v>
+        <v>45162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8318,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8361,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8366,14 +8371,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45392</v>
+        <v>45628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8391,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8434,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8448,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45600</v>
+        <v>45628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8459,7 +8464,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8519,7 +8524,7 @@
         <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8580,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8594,10 +8599,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45728</v>
+        <v>46266</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8609,13 +8614,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 31291-2026</t>
+          <t>A 951-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46218</v>
+        <v>45301</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1419,11 +1419,16 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>28.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1453,154 +1458,149 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare
+Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31291-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sandödla
 Hasselmus</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 951-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Bredbrämad bastardsvärmare
-Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45600</v>
+        <v>45318</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,17 +1742,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1778,46 +1778,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45318</v>
+        <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,16 +1847,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1880,49 +1880,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45407</v>
+        <v>46114</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1985,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1996,38 +1996,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44844</v>
+        <v>46125</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2081,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2097,35 +2097,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46114</v>
+        <v>45434</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2305,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2316,38 +2316,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46114</v>
+        <v>45600</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2410,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2421,38 +2421,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46125</v>
+        <v>46183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,20 +2482,20 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>6.2</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2522,42 +2522,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45434</v>
+        <v>44844</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,20 +2587,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2611,10 +2611,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2627,42 +2627,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2672,14 +2672,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46183</v>
+        <v>46258</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2692,19 +2692,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2732,35 +2732,39 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
@@ -2784,7 +2788,7 @@
         <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2877,7 +2881,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2887,14 +2891,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46258</v>
+        <v>45407</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2907,7 +2911,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2916,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2931,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2947,39 +2951,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44922</v>
+        <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45572</v>
+        <v>45755</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45318</v>
+        <v>45324</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,8 +3522,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3566,7 +3571,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44827</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3595,8 +3600,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>18.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3639,7 +3649,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,10 +3663,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45324</v>
+        <v>45555</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3668,13 +3678,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3722,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3736,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45162</v>
+        <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3752,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3795,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3809,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45728</v>
+        <v>45498</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3825,7 +3830,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3868,7 +3873,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45180</v>
+        <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3898,7 +3903,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3941,7 +3946,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3955,10 +3960,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44978</v>
+        <v>45343</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3971,7 +3976,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4014,7 +4019,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4024,14 +4029,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45652</v>
+        <v>45700</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4044,7 +4049,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4087,7 +4092,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4101,10 +4106,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45740</v>
+        <v>45818</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4117,7 +4122,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4160,7 +4165,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4174,10 +4179,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45336</v>
+        <v>44657</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4189,8 +4194,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4233,7 +4243,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4247,10 +4257,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45397</v>
+        <v>45426</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4262,8 +4272,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4306,7 +4321,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4320,10 +4335,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45818</v>
+        <v>45875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4336,7 +4351,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4379,7 +4394,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4389,14 +4404,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45700</v>
+        <v>46035</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4409,7 +4424,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4452,7 +4467,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4466,10 +4481,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45875</v>
+        <v>44923</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4482,7 +4497,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4525,7 +4540,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4539,10 +4554,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45600</v>
+        <v>45971</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4555,7 +4570,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4615,7 +4630,7 @@
         <v>45273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4671,7 +4686,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4685,10 +4700,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44845</v>
+        <v>45993</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4700,8 +4715,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4744,7 +4764,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4758,10 +4778,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45971</v>
+        <v>45740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4774,7 +4794,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4817,7 +4837,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4831,10 +4851,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45769</v>
+        <v>45043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4847,7 +4867,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4890,7 +4910,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4904,10 +4924,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45993</v>
+        <v>45317</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4919,13 +4939,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>7.8</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4968,7 +4983,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4982,10 +4997,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45343</v>
+        <v>45547</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4998,7 +5013,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5041,7 +5056,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5055,10 +5070,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46035</v>
+        <v>45429</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5071,7 +5086,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5114,7 +5129,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5128,10 +5143,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44943</v>
+        <v>45392</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5144,7 +5159,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.1</v>
+        <v>5.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5187,7 +5202,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5201,10 +5216,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45180</v>
+        <v>45392</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5217,7 +5232,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5260,7 +5275,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5274,10 +5289,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45343</v>
+        <v>45112</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5295,7 +5310,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>10.6</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5338,7 +5353,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5352,10 +5367,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45320</v>
+        <v>45336</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5368,7 +5383,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5411,7 +5426,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5425,10 +5440,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45547</v>
+        <v>45838</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5441,7 +5456,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5484,7 +5499,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5498,10 +5513,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45317</v>
+        <v>45318</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5514,7 +5529,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5557,7 +5572,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5571,10 +5586,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45392</v>
+        <v>45318</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5587,7 +5602,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5630,7 +5645,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5644,10 +5659,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45392</v>
+        <v>45348</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5660,7 +5675,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5703,7 +5718,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5717,10 +5732,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45112</v>
+        <v>45532</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5732,13 +5747,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5781,7 +5791,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5795,10 +5805,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45838</v>
+        <v>45318</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5811,7 +5821,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5854,7 +5864,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5868,10 +5878,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45318</v>
+        <v>45162</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5884,7 +5894,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5927,7 +5937,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5941,10 +5951,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45318</v>
+        <v>45180</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5957,7 +5967,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6017,7 +6027,7 @@
         <v>45061</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6073,7 +6083,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6087,10 +6097,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44876</v>
+        <v>45569</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6146,7 +6156,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6160,10 +6170,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45555</v>
+        <v>45334</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6176,7 +6186,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6219,7 +6229,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6233,10 +6243,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45429</v>
+        <v>45162</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6249,7 +6259,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6292,7 +6302,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6306,10 +6316,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45498</v>
+        <v>45092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6321,13 +6331,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6370,7 +6375,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6384,10 +6389,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44903</v>
+        <v>45628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6400,7 +6405,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6443,7 +6448,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6457,10 +6462,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45569</v>
+        <v>45755</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6473,7 +6478,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6516,7 +6521,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6530,10 +6535,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45392</v>
+        <v>46006</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6546,7 +6551,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6606,7 +6611,7 @@
         <v>45875</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6662,7 +6667,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6676,10 +6681,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46006</v>
+        <v>44720</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6735,7 +6740,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6749,10 +6754,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44657</v>
+        <v>45318</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6764,13 +6769,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6813,7 +6813,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45348</v>
+        <v>45399</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6886,7 +6886,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6900,10 +6900,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45043</v>
+        <v>45397</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6959,7 +6959,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45318</v>
+        <v>45162</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45162</v>
+        <v>46125</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7105,7 +7105,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46125</v>
+        <v>45343</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7134,8 +7134,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>10.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7178,7 +7183,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7192,10 +7197,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44720</v>
+        <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7208,7 +7213,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7251,7 +7256,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7265,10 +7270,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45755</v>
+        <v>45652</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7281,7 +7286,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7324,7 +7329,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7338,10 +7343,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45532</v>
+        <v>45318</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7354,7 +7359,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7397,7 +7402,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7407,14 +7412,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45320</v>
+        <v>45628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7427,7 +7432,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7470,7 +7475,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7484,10 +7489,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44923</v>
+        <v>44903</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7500,7 +7505,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7543,7 +7548,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7557,10 +7562,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45434</v>
+        <v>44922</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7572,8 +7577,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7616,7 +7626,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7630,10 +7640,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45334</v>
+        <v>44876</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7646,7 +7656,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7689,7 +7699,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7703,10 +7713,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45329</v>
+        <v>45434</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7718,13 +7728,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7767,7 +7772,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7781,10 +7786,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45330</v>
+        <v>45320</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7796,13 +7801,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>18.4</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45089</v>
+        <v>44943</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45426</v>
+        <v>45572</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7947,13 +7947,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7996,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8010,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45399</v>
+        <v>44827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8026,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8069,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8083,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45755</v>
+        <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8099,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>14</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8142,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8156,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45092</v>
+        <v>45180</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8172,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8215,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8229,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45318</v>
+        <v>45769</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8245,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8288,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8302,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45162</v>
+        <v>45392</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8318,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8361,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8371,14 +8366,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45628</v>
+        <v>45600</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8391,7 +8386,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8434,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8448,10 +8443,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45628</v>
+        <v>46266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8464,7 +8459,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8524,7 +8519,7 @@
         <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8585,7 +8580,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8599,10 +8594,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46266</v>
+        <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8614,8 +8609,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7716-2024</t>
+          <t>A 951-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45349</v>
+        <v>45301</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1309,8 +1309,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>28.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1319,10 +1324,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1337,164 +1342,159 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
       </c>
       <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare
+Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7716-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Ängskovall</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 951-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Bredbrämad bastardsvärmare
-Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
         <v/>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
         <v>46218</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45318</v>
+        <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,16 +1742,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1778,46 +1778,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46114</v>
+        <v>45434</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1891,38 +1891,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46114</v>
+        <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,20 +1952,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1976,58 +1976,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46125</v>
+        <v>45069</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2056,8 +2056,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>11.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2069,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2081,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2097,35 +2102,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
@@ -2149,7 +2154,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2247,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45434</v>
+        <v>45318</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,17 +2277,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2296,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2308,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45600</v>
+        <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,7 +2382,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2421,38 +2426,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46183</v>
+        <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,10 +2487,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2494,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2506,58 +2511,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2571,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44844</v>
+        <v>46114</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,10 +2592,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2599,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2611,58 +2616,58 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2672,14 +2677,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46258</v>
+        <v>46125</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2692,7 +2697,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2701,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2716,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2732,46 +2737,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2785,10 +2786,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45069</v>
+        <v>46183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2800,16 +2801,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>11.4</v>
+        <v>6.2</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2846,42 +2842,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2891,14 +2887,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45407</v>
+        <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2911,7 +2907,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2920,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2935,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2951,35 +2947,39 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45329</v>
+        <v>45600</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,13 +3371,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3415,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,10 +3429,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45755</v>
+        <v>45273</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3450,7 +3445,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3488,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3502,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45324</v>
+        <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,13 +3517,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>14</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3571,7 +3561,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3575,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3600,13 +3590,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>18.4</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3649,7 +3634,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3663,10 +3648,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45555</v>
+        <v>45334</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3679,7 +3664,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3722,7 +3707,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3736,10 +3721,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44978</v>
+        <v>45329</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3751,8 +3736,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3795,7 +3785,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3809,10 +3799,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45498</v>
+        <v>45769</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3824,13 +3814,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3873,7 +3858,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3887,10 +3872,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45089</v>
+        <v>45498</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3902,8 +3887,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3946,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3960,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45343</v>
+        <v>45572</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3976,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4019,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4029,14 +4019,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45700</v>
+        <v>44922</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4048,8 +4038,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4092,7 +4087,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4106,10 +4101,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45818</v>
+        <v>45330</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4121,8 +4116,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>6.7</v>
+        <v>18.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4165,7 +4165,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44657</v>
+        <v>45089</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4194,13 +4194,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4260,7 +4255,7 @@
         <v>45426</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4321,7 +4316,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4335,10 +4330,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45875</v>
+        <v>45399</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4351,7 +4346,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4394,7 +4389,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4408,10 +4403,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46035</v>
+        <v>44903</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4424,7 +4419,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4467,7 +4462,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4481,10 +4476,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44923</v>
+        <v>45569</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4497,7 +4492,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4540,7 +4535,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4554,10 +4549,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45971</v>
+        <v>44827</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4570,7 +4565,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4613,7 +4608,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4627,10 +4622,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45273</v>
+        <v>45392</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4643,7 +4638,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4686,7 +4681,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4700,10 +4695,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45993</v>
+        <v>45343</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4715,13 +4710,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4764,7 +4754,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4778,10 +4768,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45740</v>
+        <v>45755</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4794,7 +4784,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4837,7 +4827,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4851,10 +4841,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45043</v>
+        <v>45318</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4867,7 +4857,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4910,7 +4900,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4924,10 +4914,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45317</v>
+        <v>45092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4940,7 +4930,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4983,7 +4973,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4997,10 +4987,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45547</v>
+        <v>44657</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5012,8 +5002,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5056,7 +5051,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5070,10 +5065,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45429</v>
+        <v>44943</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5086,7 +5081,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5129,7 +5124,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5143,10 +5138,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45392</v>
+        <v>45180</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5159,7 +5154,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5202,7 +5197,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5216,10 +5211,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45392</v>
+        <v>45348</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5232,7 +5227,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5275,7 +5270,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5289,10 +5284,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45112</v>
+        <v>45043</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5304,13 +5299,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5353,7 +5343,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5367,10 +5357,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45336</v>
+        <v>45324</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5382,8 +5372,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5426,7 +5421,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5440,10 +5435,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45838</v>
+        <v>45162</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5456,7 +5451,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5499,7 +5494,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5513,10 +5508,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45318</v>
+        <v>45343</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5528,8 +5523,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>10.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5589,7 +5589,7 @@
         <v>45318</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5645,7 +5645,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5659,10 +5659,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45348</v>
+        <v>45180</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5718,7 +5718,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45532</v>
+        <v>44978</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5791,7 +5791,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45318</v>
+        <v>45162</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5864,7 +5864,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5874,14 +5874,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45162</v>
+        <v>45628</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5951,10 +5951,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45180</v>
+        <v>45628</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6010,7 +6010,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45061</v>
+        <v>45204</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6039,8 +6039,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6083,7 +6088,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6097,10 +6102,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45569</v>
+        <v>45318</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6113,7 +6118,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6156,7 +6161,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6170,10 +6175,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45334</v>
+        <v>45652</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6186,7 +6191,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6229,7 +6234,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6243,10 +6248,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45162</v>
+        <v>45728</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6258,8 +6263,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6302,7 +6312,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6316,10 +6326,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45092</v>
+        <v>45162</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6332,7 +6342,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6375,7 +6385,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6389,10 +6399,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45628</v>
+        <v>45320</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6405,7 +6415,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7.5</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6448,7 +6458,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6462,10 +6472,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45755</v>
+        <v>45740</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6478,7 +6488,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6521,7 +6531,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6535,10 +6545,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46006</v>
+        <v>44720</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6594,7 +6604,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6608,10 +6618,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45875</v>
+        <v>45336</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6624,7 +6634,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6667,7 +6677,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6681,10 +6691,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44720</v>
+        <v>45547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6697,7 +6707,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6740,7 +6750,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6754,10 +6764,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45318</v>
+        <v>45755</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6770,7 +6780,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6813,7 +6823,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6827,10 +6837,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45399</v>
+        <v>45317</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6843,7 +6853,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6886,7 +6896,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6900,10 +6910,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45397</v>
+        <v>45532</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6916,7 +6926,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6959,7 +6969,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6973,10 +6983,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45162</v>
+        <v>45320</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6989,7 +6999,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7032,7 +7042,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7046,10 +7056,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46125</v>
+        <v>44923</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7062,7 +7072,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7105,7 +7115,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7119,10 +7129,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45343</v>
+        <v>45397</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7134,13 +7144,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>10.6</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7183,7 +7188,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7197,10 +7202,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45320</v>
+        <v>45434</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7213,7 +7218,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7256,7 +7261,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7270,10 +7275,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45652</v>
+        <v>45392</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7286,7 +7291,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7329,7 +7334,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7343,10 +7348,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45318</v>
+        <v>45392</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7359,7 +7364,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7402,7 +7407,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7412,14 +7417,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45628</v>
+        <v>45318</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7432,7 +7437,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7475,7 +7480,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7489,10 +7494,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44903</v>
+        <v>45318</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7505,7 +7510,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7548,7 +7553,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7562,10 +7567,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44922</v>
+        <v>45061</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7577,13 +7582,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7626,7 +7626,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7636,14 +7636,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44876</v>
+        <v>45700</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45434</v>
+        <v>44876</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7772,7 +7772,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7786,10 +7786,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45320</v>
+        <v>45555</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44943</v>
+        <v>45875</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45572</v>
+        <v>45818</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44827</v>
+        <v>45971</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44845</v>
+        <v>45993</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8093,8 +8093,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8142,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8156,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45180</v>
+        <v>46035</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8172,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8215,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8229,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45769</v>
+        <v>45112</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8239,8 +8244,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8293,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8307,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45392</v>
+        <v>45838</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8323,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8366,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8370,10 +8380,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45600</v>
+        <v>45875</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8396,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8439,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8453,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46266</v>
+        <v>46006</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8459,7 +8469,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8502,7 +8512,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8516,10 +8526,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45204</v>
+        <v>46125</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8531,13 +8541,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8580,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8594,10 +8599,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45728</v>
+        <v>46266</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8609,13 +8614,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 951-2024</t>
+          <t>A 31291-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45301</v>
+        <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1309,16 +1309,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>28.1</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1348,259 +1343,264 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Sandödla
+Hasselmus</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7716-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Ängskovall</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 951-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bredbrämad bastardsvärmare
 Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 7716-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Ängskovall</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31291-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Sandödla
-Hasselmus</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45600</v>
+        <v>46114</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1786,38 +1786,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45434</v>
+        <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1891,38 +1891,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44844</v>
+        <v>46125</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45069</v>
+        <v>45318</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2056,25 +2056,20 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>11.4</v>
+        <v>6.8</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2089,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2098,39 +2093,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
@@ -2154,7 +2149,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2247,7 +2242,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2256,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45318</v>
+        <v>45434</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2277,16 +2272,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2301,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2313,46 +2308,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45407</v>
+        <v>45600</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,7 +2377,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2426,38 +2421,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46114</v>
+        <v>46183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2487,20 +2482,20 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -2511,58 +2506,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2572,14 +2567,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46114</v>
+        <v>46258</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2592,7 +2587,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2601,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2616,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2625,49 +2620,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2681,10 +2680,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46125</v>
+        <v>44844</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2697,20 +2696,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2721,10 +2720,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2737,42 +2736,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2786,10 +2785,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46183</v>
+        <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2801,11 +2800,16 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>11.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2842,42 +2846,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2887,14 +2891,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46258</v>
+        <v>45407</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2907,7 +2911,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2916,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2931,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2947,39 +2951,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45600</v>
+        <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,8 +3371,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3415,7 +3420,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3429,10 +3434,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45273</v>
+        <v>45755</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3445,7 +3450,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3488,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3502,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44845</v>
+        <v>45324</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3517,8 +3522,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>14</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3561,7 +3571,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3575,10 +3585,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45429</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3590,8 +3600,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>18.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3634,7 +3649,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3648,10 +3663,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45334</v>
+        <v>45555</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3664,7 +3679,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3707,7 +3722,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3721,10 +3736,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45329</v>
+        <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3736,13 +3751,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3785,7 +3795,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3799,10 +3809,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45769</v>
+        <v>45498</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3814,8 +3824,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3858,7 +3873,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3872,10 +3887,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45498</v>
+        <v>46035</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3887,13 +3902,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3946,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3960,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45572</v>
+        <v>45089</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3976,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4019,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4033,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44922</v>
+        <v>45343</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4038,13 +4048,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4087,7 +4092,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4101,10 +4106,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45330</v>
+        <v>45818</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4116,13 +4121,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>18.4</v>
+        <v>6.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4165,7 +4165,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45089</v>
+        <v>44657</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4194,8 +4194,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4255,7 +4260,7 @@
         <v>45426</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4316,7 +4321,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4330,10 +4335,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45399</v>
+        <v>45971</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4346,7 +4351,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4389,7 +4394,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44903</v>
+        <v>44923</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4419,7 +4424,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4462,7 +4467,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4476,10 +4481,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45569</v>
+        <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4491,8 +4496,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4535,7 +4545,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4549,10 +4559,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44827</v>
+        <v>45838</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4565,7 +4575,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4608,7 +4618,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4622,10 +4632,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45392</v>
+        <v>45993</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4637,8 +4647,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>7.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4681,7 +4696,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4695,10 +4710,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45343</v>
+        <v>45273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4711,7 +4726,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4754,7 +4769,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4764,14 +4779,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45755</v>
+        <v>45700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4784,7 +4799,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4827,7 +4842,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4841,10 +4856,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45318</v>
+        <v>45740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4857,7 +4872,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4900,7 +4915,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4914,10 +4929,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45092</v>
+        <v>45043</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4930,7 +4945,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4973,7 +4988,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4987,10 +5002,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44657</v>
+        <v>45875</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5002,13 +5017,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5051,7 +5061,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5065,10 +5075,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44943</v>
+        <v>45317</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5081,7 +5091,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5124,7 +5134,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5138,10 +5148,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45180</v>
+        <v>45547</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5154,7 +5164,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5197,7 +5207,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5211,10 +5221,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45348</v>
+        <v>45429</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5227,7 +5237,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.9</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5270,7 +5280,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5284,10 +5294,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45043</v>
+        <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5300,7 +5310,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5343,7 +5353,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5357,10 +5367,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45324</v>
+        <v>45392</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5372,13 +5382,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5421,7 +5426,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5435,10 +5440,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45162</v>
+        <v>45336</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5451,7 +5456,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5494,7 +5499,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5508,10 +5513,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45343</v>
+        <v>45318</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5523,13 +5528,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>10.6</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5589,7 +5589,7 @@
         <v>45318</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5645,7 +5645,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5659,10 +5659,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45180</v>
+        <v>46006</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5718,7 +5718,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44978</v>
+        <v>45875</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5791,7 +5791,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45162</v>
+        <v>45348</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>6.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5864,7 +5864,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5874,14 +5874,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45628</v>
+        <v>45532</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5951,10 +5951,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45628</v>
+        <v>45318</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6010,7 +6010,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45204</v>
+        <v>45162</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6039,13 +6039,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6088,7 +6083,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6102,10 +6097,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45318</v>
+        <v>45180</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6118,7 +6113,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6161,7 +6156,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6175,10 +6170,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45652</v>
+        <v>45061</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6191,7 +6186,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6234,7 +6229,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6248,10 +6243,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45728</v>
+        <v>45569</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6263,13 +6258,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6312,7 +6302,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6326,10 +6316,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45162</v>
+        <v>45334</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6342,7 +6332,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6385,7 +6375,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6399,10 +6389,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45320</v>
+        <v>45162</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6415,7 +6405,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6458,7 +6448,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6472,10 +6462,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45740</v>
+        <v>45092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6488,7 +6478,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6531,7 +6521,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6545,10 +6535,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44720</v>
+        <v>45628</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6561,7 +6551,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6604,7 +6594,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6618,10 +6608,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45336</v>
+        <v>46125</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6634,7 +6624,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6677,7 +6667,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6691,10 +6681,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45547</v>
+        <v>45755</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6707,7 +6697,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6750,7 +6740,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6764,10 +6754,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45755</v>
+        <v>44720</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6780,7 +6770,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6823,7 +6813,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6837,10 +6827,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45317</v>
+        <v>45318</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6853,7 +6843,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6896,7 +6886,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6910,10 +6900,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45532</v>
+        <v>45399</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6926,7 +6916,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6969,7 +6959,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6983,10 +6973,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45320</v>
+        <v>45397</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6999,7 +6989,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7042,7 +7032,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7056,10 +7046,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44923</v>
+        <v>45162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7072,7 +7062,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7115,7 +7105,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7129,10 +7119,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45397</v>
+        <v>45343</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7144,8 +7134,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>10.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7188,7 +7183,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7202,10 +7197,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45434</v>
+        <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7218,7 +7213,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7261,7 +7256,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7275,10 +7270,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45392</v>
+        <v>45652</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7291,7 +7286,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7334,7 +7329,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7348,10 +7343,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45392</v>
+        <v>45318</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7364,7 +7359,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7407,7 +7402,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7417,14 +7412,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45318</v>
+        <v>45628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7437,7 +7432,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7480,7 +7475,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7494,10 +7489,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45318</v>
+        <v>44903</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7510,7 +7505,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7553,7 +7548,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7567,10 +7562,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45061</v>
+        <v>44922</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7582,8 +7577,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7626,7 +7626,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7636,14 +7636,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45700</v>
+        <v>44876</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44876</v>
+        <v>45434</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7772,7 +7772,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7786,10 +7786,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45555</v>
+        <v>45320</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45875</v>
+        <v>44943</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45818</v>
+        <v>45572</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.7</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45971</v>
+        <v>44827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45993</v>
+        <v>46266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8093,13 +8093,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>7.8</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8142,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8156,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46035</v>
+        <v>44845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8172,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>14</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8215,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8229,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45112</v>
+        <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8244,13 +8239,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8293,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8307,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8323,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8366,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8380,10 +8370,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45875</v>
+        <v>45392</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8396,7 +8386,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8439,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8453,10 +8443,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46006</v>
+        <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8469,7 +8459,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8512,7 +8502,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8526,10 +8516,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46125</v>
+        <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8541,8 +8531,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8585,7 +8580,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8599,10 +8594,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46266</v>
+        <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8614,8 +8609,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45349</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46114</v>
+        <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1786,38 +1786,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46114</v>
+        <v>45407</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1891,38 +1891,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46125</v>
+        <v>45318</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,17 +1952,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1988,46 +1988,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45318</v>
+        <v>46114</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,16 +2057,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2090,49 +2090,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45343</v>
+        <v>46114</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2161,16 +2161,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>22.7</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2179,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2191,58 +2186,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45434</v>
+        <v>46125</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,7 +2267,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2316,38 +2311,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45600</v>
+        <v>44844</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,20 +2372,20 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -2401,10 +2396,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2417,42 +2412,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2461,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46183</v>
+        <v>45343</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2481,8 +2476,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>22.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2518,46 +2518,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2567,14 +2567,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46258</v>
+        <v>46183</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,19 +2587,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2614,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2627,46 +2627,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2680,10 +2676,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44844</v>
+        <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,10 +2692,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2708,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2720,10 +2716,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2736,42 +2732,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2781,14 +2777,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45069</v>
+        <v>46258</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2800,13 +2796,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2815,10 +2806,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2833,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2846,42 +2837,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2895,10 +2890,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45407</v>
+        <v>45069</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2910,8 +2905,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>11.4</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2935,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2951,35 +2951,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45329</v>
+        <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,13 +3371,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3415,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,10 +3429,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45755</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3449,8 +3444,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45324</v>
+        <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,13 +3522,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3571,7 +3566,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>45318</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3600,13 +3595,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>18.4</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3649,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3663,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45555</v>
+        <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3678,8 +3668,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3722,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3736,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44978</v>
+        <v>45162</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3752,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3795,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3809,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45498</v>
+        <v>45728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3830,7 +3825,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3873,7 +3868,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3887,10 +3882,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46035</v>
+        <v>45180</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3903,7 +3898,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3946,7 +3941,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3960,10 +3955,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45089</v>
+        <v>44978</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3976,7 +3971,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4019,7 +4014,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4033,10 +4028,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45343</v>
+        <v>45652</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4049,7 +4044,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4092,7 +4087,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4106,10 +4101,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45818</v>
+        <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4122,7 +4117,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4165,7 +4160,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4179,10 +4174,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44657</v>
+        <v>45336</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4194,13 +4189,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4243,7 +4233,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4257,10 +4247,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45426</v>
+        <v>45397</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4272,13 +4262,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4321,7 +4306,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4335,10 +4320,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45971</v>
+        <v>46035</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4351,7 +4336,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4394,7 +4379,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4408,10 +4393,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44923</v>
+        <v>45818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4424,7 +4409,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4467,7 +4452,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4481,10 +4466,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45112</v>
+        <v>45600</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4496,13 +4481,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4545,7 +4525,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4559,10 +4539,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45838</v>
+        <v>45273</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4575,7 +4555,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4618,7 +4598,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4632,10 +4612,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45993</v>
+        <v>44845</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,13 +4627,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4696,7 +4671,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4710,10 +4685,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45273</v>
+        <v>45769</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4726,7 +4701,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4769,7 +4744,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4779,14 +4754,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45700</v>
+        <v>45971</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4799,7 +4774,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4842,7 +4817,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4856,10 +4831,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45740</v>
+        <v>45343</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4872,7 +4847,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4915,7 +4890,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4929,10 +4904,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45043</v>
+        <v>45993</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4944,8 +4919,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4988,7 +4968,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5002,10 +4982,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45875</v>
+        <v>44943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5018,7 +4998,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5061,7 +5041,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5075,10 +5055,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45317</v>
+        <v>45180</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5091,7 +5071,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5134,7 +5114,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5148,10 +5128,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45547</v>
+        <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5163,8 +5143,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>10.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5207,7 +5192,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5221,10 +5206,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45429</v>
+        <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5236,8 +5221,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5280,7 +5270,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5294,10 +5284,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45392</v>
+        <v>45838</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5310,7 +5300,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5353,7 +5343,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5367,10 +5357,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45392</v>
+        <v>45320</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5383,7 +5373,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5426,7 +5416,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5436,14 +5426,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45336</v>
+        <v>45700</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5456,7 +5446,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5499,7 +5489,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5513,10 +5503,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45318</v>
+        <v>45547</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5529,7 +5519,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5572,7 +5562,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5586,10 +5576,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45318</v>
+        <v>45317</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5602,7 +5592,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5645,7 +5635,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5659,10 +5649,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46006</v>
+        <v>45392</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5675,7 +5665,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5718,7 +5708,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5732,10 +5722,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45875</v>
+        <v>45392</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5748,7 +5738,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5791,7 +5781,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5805,10 +5795,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45348</v>
+        <v>45875</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5821,7 +5811,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.9</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5864,7 +5854,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5878,10 +5868,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45532</v>
+        <v>45875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5894,7 +5884,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5937,7 +5927,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5951,10 +5941,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45318</v>
+        <v>46006</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5967,7 +5957,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6010,7 +6000,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6024,10 +6014,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45162</v>
+        <v>45318</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6040,7 +6030,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6083,7 +6073,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6097,10 +6087,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45180</v>
+        <v>45318</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6113,7 +6103,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6173,7 +6163,7 @@
         <v>45061</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6229,7 +6219,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6243,10 +6233,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45569</v>
+        <v>44876</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6302,7 +6292,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6316,10 +6306,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45334</v>
+        <v>45555</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6332,7 +6322,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6375,7 +6365,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6389,10 +6379,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45162</v>
+        <v>45429</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6405,7 +6395,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6448,7 +6438,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6462,10 +6452,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45092</v>
+        <v>46125</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6478,7 +6468,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6521,7 +6511,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6535,10 +6525,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45628</v>
+        <v>45498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6550,8 +6540,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6594,7 +6589,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6608,10 +6603,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46125</v>
+        <v>44903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6624,7 +6619,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6667,7 +6662,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6681,10 +6676,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45755</v>
+        <v>45569</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6697,7 +6692,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6740,7 +6735,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6754,10 +6749,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44720</v>
+        <v>45392</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6770,7 +6765,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6813,7 +6808,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6827,10 +6822,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45318</v>
+        <v>44657</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6842,8 +6837,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6886,7 +6886,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6900,10 +6900,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45399</v>
+        <v>45348</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>6.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6959,7 +6959,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45397</v>
+        <v>45043</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45162</v>
+        <v>45318</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7105,7 +7105,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45343</v>
+        <v>45162</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7134,13 +7134,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>10.6</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7183,7 +7178,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7197,10 +7192,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45320</v>
+        <v>44720</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7213,7 +7208,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7256,7 +7251,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7270,10 +7265,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45652</v>
+        <v>45755</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7286,7 +7281,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7329,7 +7324,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7343,10 +7338,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45318</v>
+        <v>46266</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7359,7 +7354,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7402,7 +7397,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7412,14 +7407,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45628</v>
+        <v>45532</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7432,7 +7427,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7475,7 +7470,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7489,10 +7484,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44903</v>
+        <v>45320</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7505,7 +7500,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7548,7 +7543,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7562,10 +7557,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44922</v>
+        <v>44923</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7577,13 +7572,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7626,7 +7616,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7640,10 +7630,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44876</v>
+        <v>45434</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7656,7 +7646,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7699,7 +7689,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7713,10 +7703,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45434</v>
+        <v>45334</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7729,7 +7719,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7772,7 +7762,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7786,10 +7776,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45320</v>
+        <v>45329</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7801,8 +7791,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7840,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7854,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44943</v>
+        <v>45330</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7874,8 +7869,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.1</v>
+        <v>18.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45572</v>
+        <v>45089</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44827</v>
+        <v>45426</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8020,8 +8020,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8069,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8083,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46266</v>
+        <v>45399</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8099,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8142,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8156,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44845</v>
+        <v>45755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8172,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>14</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8215,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8229,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45180</v>
+        <v>45092</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8245,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8288,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8302,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45769</v>
+        <v>45318</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8318,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8361,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8370,10 +8375,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45392</v>
+        <v>45162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8391,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8434,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8439,14 +8444,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45600</v>
+        <v>45628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8459,7 +8464,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8502,7 +8507,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8516,10 +8521,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45204</v>
+        <v>45628</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8531,13 +8536,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45728</v>
+        <v>45204</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45349</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45407</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45318</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>46114</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>46114</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>46125</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44844</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45343</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>46183</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>46258</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45069</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45318</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45162</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45180</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44978</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>45652</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>45336</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45397</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>46035</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45600</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45273</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44845</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45769</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45971</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45343</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45993</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>44943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>45180</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>45838</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45320</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45700</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45547</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45317</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45392</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45392</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45875</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>46006</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45318</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45318</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45061</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44876</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>45555</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45429</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>46125</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45569</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>45392</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44657</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45348</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>45043</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>45318</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>45162</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>44720</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>45755</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>46266</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>45532</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>45320</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44923</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45434</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>45334</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45329</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>45330</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>45089</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45426</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45399</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45092</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45318</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45628</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45204</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45349</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45407</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45318</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>46114</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>46114</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>46125</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44844</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45343</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>46183</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>46258</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45069</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>44827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45318</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45162</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45180</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44978</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>45652</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>45336</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45397</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>46035</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45600</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45273</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44845</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45769</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45971</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45343</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45993</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>44943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>45180</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>45838</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45320</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45700</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45547</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45317</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45392</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45392</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45875</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>46006</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45318</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45318</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45061</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44876</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>45555</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45429</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>46125</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45569</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>45392</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44657</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45348</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>45043</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>45318</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>45162</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>44720</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>45755</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>46266</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>45532</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>45320</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44923</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45434</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>45334</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45329</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>45330</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>45089</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45426</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45399</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45092</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45318</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45628</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45204</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31291-2026</t>
+          <t>A 7716-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46218</v>
+        <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1346,150 +1346,150 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Ängskovall</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 31291-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Sandödla
 Hasselmus</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 7716-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Ängskovall</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
         <v/>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45600</v>
+        <v>45318</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,17 +1742,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1778,46 +1778,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45407</v>
+        <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1891,38 +1891,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45318</v>
+        <v>46114</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1985,49 +1985,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2090,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2101,38 +2101,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46114</v>
+        <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2161,21 +2161,26 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>22.7</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2186,58 +2191,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2256,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46125</v>
+        <v>45434</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2267,7 +2272,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2311,38 +2316,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44844</v>
+        <v>45600</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2384,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2396,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2412,42 +2417,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2461,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45343</v>
+        <v>46183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2476,13 +2481,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>22.7</v>
+        <v>6.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2518,46 +2518,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46183</v>
+        <v>44844</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2627,42 +2627,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45434</v>
+        <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2691,8 +2691,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>11.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2704,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2716,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2732,42 +2737,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34703-2026</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2777,14 +2782,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46258</v>
+        <v>45407</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2797,7 +2802,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2806,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2821,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2837,46 +2842,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 34703-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2886,14 +2887,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45069</v>
+        <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2905,13 +2906,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2920,10 +2916,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2938,7 +2934,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2951,35 +2947,39 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 34703-2026 artfynd.xlsx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 34703-2026 karta.png", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 34703-2026 georefererad karta.tif", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 34703-2026 FSC-klagomål.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 34703-2026 FSC-klagomål mail.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 34703-2026 tillsynsbegäran.docx", "A 34703-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 34703-2026 tillsynsbegäran mail.docx", "A 34703-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 34703-2026 prioriterade fågelarter.docx", "A 34703-2026")</f>
         <v/>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45572</v>
+        <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,8 +3371,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3415,7 +3420,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3429,10 +3434,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>45755</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3444,13 +3449,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44827</v>
+        <v>45324</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,8 +3522,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3566,7 +3571,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45318</v>
+        <v>45555</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3596,7 +3601,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3639,7 +3644,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,10 +3658,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45324</v>
+        <v>45330</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3679,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>18.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3722,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3736,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45162</v>
+        <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3752,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3795,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3809,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45728</v>
+        <v>45498</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3825,7 +3830,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3868,7 +3873,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45180</v>
+        <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3898,7 +3903,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3941,7 +3946,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3955,10 +3960,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44978</v>
+        <v>45343</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3971,7 +3976,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4014,7 +4019,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4024,14 +4029,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45652</v>
+        <v>45700</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4044,7 +4049,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4087,7 +4092,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4101,10 +4106,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45740</v>
+        <v>46035</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4117,7 +4122,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4160,7 +4165,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4174,10 +4179,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45336</v>
+        <v>44657</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4189,8 +4194,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4233,7 +4243,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4247,10 +4257,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45397</v>
+        <v>45426</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4262,8 +4272,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4306,7 +4321,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4320,10 +4335,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46035</v>
+        <v>45875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4336,7 +4351,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4379,7 +4394,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4393,10 +4408,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45818</v>
+        <v>44923</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4409,7 +4424,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4452,7 +4467,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4466,10 +4481,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45600</v>
+        <v>45818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4482,7 +4497,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4542,7 +4557,7 @@
         <v>45273</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4598,7 +4613,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4612,10 +4627,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44845</v>
+        <v>45971</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4628,7 +4643,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4671,7 +4686,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4685,10 +4700,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45769</v>
+        <v>45740</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4701,7 +4716,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4744,7 +4759,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4758,10 +4773,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45971</v>
+        <v>45043</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4774,7 +4789,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4817,7 +4832,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4831,10 +4846,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45343</v>
+        <v>45317</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4847,7 +4862,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4907,7 +4922,7 @@
         <v>45993</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4968,7 +4983,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4982,10 +4997,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44943</v>
+        <v>45112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4997,8 +5012,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5041,7 +5061,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5055,10 +5075,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45180</v>
+        <v>45838</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5071,7 +5091,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5114,7 +5134,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5128,10 +5148,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45343</v>
+        <v>45547</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5143,13 +5163,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>10.6</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5192,7 +5207,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5206,10 +5221,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45112</v>
+        <v>45429</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5221,13 +5236,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5270,7 +5280,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5284,10 +5294,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45838</v>
+        <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5300,7 +5310,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5343,7 +5353,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5357,10 +5367,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45320</v>
+        <v>45392</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5373,7 +5383,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5416,7 +5426,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5426,14 +5436,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45700</v>
+        <v>45336</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5446,7 +5456,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5489,7 +5499,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5503,10 +5513,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45547</v>
+        <v>45318</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5519,7 +5529,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5562,7 +5572,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5576,10 +5586,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45317</v>
+        <v>45318</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5592,7 +5602,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5635,7 +5645,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5649,10 +5659,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45392</v>
+        <v>45348</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5665,7 +5675,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5708,7 +5718,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5722,10 +5732,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45392</v>
+        <v>45532</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5738,7 +5748,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5781,7 +5791,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5795,10 +5805,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45875</v>
+        <v>45318</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5811,7 +5821,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5854,7 +5864,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5868,10 +5878,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45875</v>
+        <v>45162</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5884,7 +5894,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5927,7 +5937,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5941,10 +5951,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46006</v>
+        <v>45180</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5957,7 +5967,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6000,7 +6010,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6014,10 +6024,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45318</v>
+        <v>45061</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6030,7 +6040,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6073,7 +6083,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6087,10 +6097,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45318</v>
+        <v>45569</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6103,7 +6113,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6146,7 +6156,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6160,10 +6170,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45061</v>
+        <v>45334</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6176,7 +6186,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6219,7 +6229,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6233,10 +6243,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44876</v>
+        <v>45162</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6249,7 +6259,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6292,7 +6302,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6306,10 +6316,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45555</v>
+        <v>46006</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6322,7 +6332,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6365,7 +6375,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6379,10 +6389,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45429</v>
+        <v>45875</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6395,7 +6405,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6438,7 +6448,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6452,10 +6462,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46125</v>
+        <v>45092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6468,7 +6478,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6511,7 +6521,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6525,10 +6535,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45498</v>
+        <v>45628</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6540,13 +6550,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6589,7 +6594,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6603,10 +6608,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44903</v>
+        <v>45755</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6619,7 +6624,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6662,7 +6667,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6676,10 +6681,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45569</v>
+        <v>44720</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6692,7 +6697,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6735,7 +6740,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6749,10 +6754,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45392</v>
+        <v>46125</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6765,7 +6770,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6808,7 +6813,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6822,10 +6827,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44657</v>
+        <v>45318</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,13 +6842,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6886,7 +6886,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6900,10 +6900,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45348</v>
+        <v>45399</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6959,7 +6959,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45043</v>
+        <v>45397</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45318</v>
+        <v>45162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7105,7 +7105,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45162</v>
+        <v>45343</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7134,8 +7134,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>10.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7178,7 +7183,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7192,10 +7197,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44720</v>
+        <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7208,7 +7213,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7251,7 +7256,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7265,10 +7270,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45755</v>
+        <v>45652</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7281,7 +7286,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7324,7 +7329,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7338,10 +7343,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46266</v>
+        <v>45318</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7354,7 +7359,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7397,7 +7402,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7407,14 +7412,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45532</v>
+        <v>45628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7427,7 +7432,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7470,7 +7475,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7484,10 +7489,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45320</v>
+        <v>44903</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7500,7 +7505,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7543,7 +7548,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7557,10 +7562,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44923</v>
+        <v>44922</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7572,8 +7577,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7616,7 +7626,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7630,10 +7640,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45434</v>
+        <v>44876</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7646,7 +7656,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7689,7 +7699,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7703,10 +7713,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45334</v>
+        <v>45434</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7719,7 +7729,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7762,7 +7772,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7776,10 +7786,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45329</v>
+        <v>45320</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7791,13 +7801,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7840,7 +7845,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7854,10 +7859,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45330</v>
+        <v>44943</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7869,13 +7874,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>18.4</v>
+        <v>0.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45089</v>
+        <v>45572</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45426</v>
+        <v>44827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8020,13 +8020,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8069,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8083,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45399</v>
+        <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8099,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>14</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8142,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8156,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45755</v>
+        <v>45180</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8172,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8215,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8229,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45092</v>
+        <v>45769</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8245,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8288,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8302,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45318</v>
+        <v>45392</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8318,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8361,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8375,10 +8370,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45162</v>
+        <v>46266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8391,7 +8386,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8434,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8444,14 +8439,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45628</v>
+        <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8464,7 +8459,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8507,7 +8502,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8521,10 +8516,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45628</v>
+        <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8536,8 +8531,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45204</v>
+        <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7716-2024</t>
+          <t>A 31291-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45349</v>
+        <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1346,150 +1346,150 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Sandödla
+Hasselmus</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7716-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Ängskovall</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 31291-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Sandödla
-Hasselmus</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45318</v>
+        <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,16 +1742,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1778,46 +1778,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46114</v>
+        <v>45407</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1891,38 +1891,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46114</v>
+        <v>45318</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,17 +1952,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1985,49 +1985,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46125</v>
+        <v>46114</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2090,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2101,38 +2101,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45343</v>
+        <v>46114</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2161,16 +2161,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>22.7</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2179,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2191,58 +2186,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45434</v>
+        <v>46125</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,7 +2267,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2316,38 +2311,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45600</v>
+        <v>44844</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,20 +2372,20 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -2401,10 +2396,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2417,35 +2412,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
@@ -2469,7 +2464,7 @@
         <v>46183</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2557,7 +2552,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2571,10 +2566,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44844</v>
+        <v>45343</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2586,8 +2581,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>22.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2623,46 +2623,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2691,13 +2691,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>11.4</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2709,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2721,10 +2716,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2737,42 +2732,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2786,10 +2781,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45407</v>
+        <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2801,8 +2796,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>11.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2826,10 +2826,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2842,35 +2842,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45329</v>
+        <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,13 +3371,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3415,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,10 +3429,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45755</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3449,8 +3444,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45324</v>
+        <v>45318</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3522,13 +3522,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3571,7 +3566,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45555</v>
+        <v>44827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3644,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3658,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45330</v>
+        <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3679,7 +3674,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>18.4</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3722,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3736,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44978</v>
+        <v>45162</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3752,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3795,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3809,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45498</v>
+        <v>45180</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3824,13 +3819,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3873,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3887,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45089</v>
+        <v>44978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3903,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3946,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3960,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45343</v>
+        <v>45652</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3976,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4019,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4029,14 +4019,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45700</v>
+        <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4049,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4092,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4106,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46035</v>
+        <v>45336</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4122,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4165,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4179,10 +4169,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44657</v>
+        <v>45397</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4194,13 +4184,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4243,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4257,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45426</v>
+        <v>46035</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4272,13 +4257,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4321,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4335,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45875</v>
+        <v>45600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4351,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4394,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4408,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44923</v>
+        <v>45273</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4424,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4467,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4481,10 +4461,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45818</v>
+        <v>44845</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4497,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.7</v>
+        <v>14</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4540,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4554,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45273</v>
+        <v>45769</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4570,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4613,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4627,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45971</v>
+        <v>45343</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4643,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4686,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4700,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45740</v>
+        <v>45818</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4716,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4759,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4769,14 +4749,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45043</v>
+        <v>45700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4789,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4832,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4846,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45317</v>
+        <v>45875</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4862,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4905,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4919,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45993</v>
+        <v>45971</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4934,13 +4914,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>7.8</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4983,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4997,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45112</v>
+        <v>44943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5012,13 +4987,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5061,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5075,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45838</v>
+        <v>45180</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5091,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5134,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5148,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45547</v>
+        <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5163,8 +5133,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>10.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5207,7 +5182,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5221,10 +5196,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45429</v>
+        <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5236,8 +5211,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5280,7 +5260,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5294,10 +5274,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45392</v>
+        <v>45993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5309,8 +5289,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5353,7 +5338,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5367,10 +5352,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45392</v>
+        <v>45838</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5383,7 +5368,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5426,7 +5411,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5440,10 +5425,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45336</v>
+        <v>45875</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5456,7 +5441,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5499,7 +5484,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5513,10 +5498,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45318</v>
+        <v>46006</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5529,7 +5514,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5572,7 +5557,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5586,10 +5571,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45318</v>
+        <v>46125</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5602,7 +5587,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5645,7 +5630,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5659,10 +5644,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45348</v>
+        <v>45320</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5675,7 +5660,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.9</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5718,7 +5703,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5732,10 +5717,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45532</v>
+        <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5748,7 +5733,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5791,7 +5776,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5805,10 +5790,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45318</v>
+        <v>45317</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5864,7 +5849,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5878,10 +5863,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45162</v>
+        <v>45392</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5894,7 +5879,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5937,7 +5922,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5951,10 +5936,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45180</v>
+        <v>45392</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5967,7 +5952,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6010,7 +5995,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6024,10 +6009,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45061</v>
+        <v>45318</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6040,7 +6025,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6083,7 +6068,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6097,10 +6082,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45569</v>
+        <v>45318</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6113,7 +6098,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6156,7 +6141,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6170,10 +6155,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45334</v>
+        <v>45061</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6186,7 +6171,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6229,7 +6214,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6243,10 +6228,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45162</v>
+        <v>44876</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6259,7 +6244,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6302,7 +6287,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6316,10 +6301,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46006</v>
+        <v>45555</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6332,7 +6317,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6375,7 +6360,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6389,10 +6374,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45875</v>
+        <v>45429</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6405,7 +6390,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6448,7 +6433,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6462,10 +6447,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45092</v>
+        <v>45498</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6477,8 +6462,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6521,7 +6511,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6535,10 +6525,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45628</v>
+        <v>44903</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6551,7 +6541,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6594,7 +6584,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6608,10 +6598,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45755</v>
+        <v>45569</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6624,7 +6614,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6667,7 +6657,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6681,10 +6671,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44720</v>
+        <v>45392</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6697,7 +6687,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6740,7 +6730,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6754,10 +6744,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46125</v>
+        <v>44657</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6769,8 +6759,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6813,7 +6808,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6827,10 +6822,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45318</v>
+        <v>45348</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6843,7 +6838,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6886,7 +6881,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6900,10 +6895,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45399</v>
+        <v>45043</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6916,7 +6911,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6959,7 +6954,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6973,10 +6968,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45397</v>
+        <v>45318</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6989,7 +6984,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7032,7 +7027,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7049,7 +7044,7 @@
         <v>45162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7062,7 +7057,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7105,7 +7100,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7119,10 +7114,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45343</v>
+        <v>44720</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7134,13 +7129,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>10.6</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7183,7 +7173,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7197,10 +7187,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45320</v>
+        <v>45755</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7256,7 +7246,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7270,10 +7260,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45652</v>
+        <v>45532</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7286,7 +7276,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7329,7 +7319,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7343,10 +7333,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45318</v>
+        <v>45320</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7359,7 +7349,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7402,7 +7392,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7412,14 +7402,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45628</v>
+        <v>44923</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7432,7 +7422,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7475,7 +7465,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7489,10 +7479,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44903</v>
+        <v>45434</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7505,7 +7495,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7548,7 +7538,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7562,10 +7552,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44922</v>
+        <v>46266</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7577,13 +7567,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7626,7 +7611,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7640,10 +7625,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44876</v>
+        <v>45334</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7656,7 +7641,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7699,7 +7684,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7713,10 +7698,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45434</v>
+        <v>45329</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7728,8 +7713,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7772,7 +7762,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7786,10 +7776,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45320</v>
+        <v>45330</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7801,8 +7791,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>18.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7845,7 +7840,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7859,10 +7854,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44943</v>
+        <v>45089</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7875,7 +7870,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7913,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7927,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45572</v>
+        <v>45426</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7947,8 +7942,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44827</v>
+        <v>45399</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44845</v>
+        <v>45755</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>14</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45180</v>
+        <v>45092</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45769</v>
+        <v>45318</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45392</v>
+        <v>45162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8366,14 +8366,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46266</v>
+        <v>45628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8443,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45600</v>
+        <v>45628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8519,7 +8519,7 @@
         <v>45204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31291-2026</t>
+          <t>A 7716-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46218</v>
+        <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1346,261 +1346,261 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Ängskovall</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 951-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare
+Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31291-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sandödla
 Hasselmus</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 7716-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Ängskovall</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7716-2024 artfynd.xlsx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7716-2024 karta.png", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7716-2024 georefererad karta.tif", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7716-2024 FSC-klagomål.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7716-2024 FSC-klagomål mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7716-2024 tillsynsbegäran.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7716-2024 tillsynsbegäran mail.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/fåglar/A 7716-2024 prioriterade fågelarter.docx", "A 7716-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 951-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Bredbrämad bastardsvärmare
-Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45600</v>
+        <v>45343</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1741,21 +1741,26 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>22.7</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -1766,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1778,46 +1783,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1836,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45407</v>
+        <v>45318</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,17 +1852,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1871,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1883,46 +1888,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45318</v>
+        <v>45434</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,16 +1957,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1976,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1988,46 +1993,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46114</v>
+        <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,7 +2062,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2090,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2101,38 +2106,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46114</v>
+        <v>46183</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,20 +2167,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2186,58 +2191,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2256,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46125</v>
+        <v>44844</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2267,20 +2272,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2291,10 +2296,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2307,42 +2312,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44844</v>
+        <v>46114</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2384,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2396,58 +2401,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2461,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46183</v>
+        <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2477,10 +2482,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2489,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2501,58 +2506,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2566,10 +2571,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45343</v>
+        <v>46125</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2581,16 +2586,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>22.7</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2611,10 +2611,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2623,46 +2623,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45434</v>
+        <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2691,8 +2691,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>11.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2704,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2716,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2732,42 +2737,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2781,10 +2786,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45069</v>
+        <v>45407</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2796,13 +2801,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>11.4</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2826,10 +2826,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2842,35 +2842,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45572</v>
+        <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,8 +3371,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3415,7 +3420,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3429,10 +3434,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3444,13 +3449,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45318</v>
+        <v>45043</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3566,7 +3566,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44827</v>
+        <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3639,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45324</v>
+        <v>45204</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45162</v>
+        <v>45728</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3746,8 +3746,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3795,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3809,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45180</v>
+        <v>45755</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3825,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3868,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3882,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44978</v>
+        <v>45547</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3898,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3941,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3955,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45652</v>
+        <v>45429</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3971,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4014,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4028,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45740</v>
+        <v>45392</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4044,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4087,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4101,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45336</v>
+        <v>45392</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4117,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4160,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4174,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45397</v>
+        <v>45324</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4184,8 +4189,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4238,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4252,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46035</v>
+        <v>45336</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4268,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4311,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4325,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45600</v>
+        <v>45318</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4341,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4384,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4398,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45273</v>
+        <v>45318</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4414,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4457,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4461,10 +4471,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44845</v>
+        <v>45330</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4476,8 +4486,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>14</v>
+        <v>18.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4535,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4549,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45769</v>
+        <v>45555</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4593,7 +4608,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4622,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45343</v>
+        <v>45348</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4638,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>6.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4681,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4695,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45818</v>
+        <v>45532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4711,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4754,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4749,14 +4764,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45700</v>
+        <v>45318</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4784,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4827,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4841,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45875</v>
+        <v>44978</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4857,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4900,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4914,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45971</v>
+        <v>45498</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4914,8 +4929,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4978,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4992,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44943</v>
+        <v>45089</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4988,7 +5008,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5051,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5065,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45180</v>
+        <v>45162</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5081,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5124,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5138,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45343</v>
+        <v>45180</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5133,13 +5153,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>10.6</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5182,7 +5197,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5196,10 +5211,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45112</v>
+        <v>45818</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5211,13 +5226,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>6.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5260,7 +5270,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5274,10 +5284,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45993</v>
+        <v>45061</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5289,13 +5299,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5338,7 +5343,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5352,10 +5357,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45838</v>
+        <v>45569</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5368,7 +5373,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5411,7 +5416,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5425,10 +5430,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45875</v>
+        <v>45334</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5441,7 +5446,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5484,7 +5489,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5494,14 +5499,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46006</v>
+        <v>45700</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5514,7 +5519,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5557,7 +5562,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5571,10 +5576,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46125</v>
+        <v>45162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5587,7 +5592,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5630,7 +5635,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5644,10 +5649,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45320</v>
+        <v>45875</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5660,7 +5665,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5703,7 +5708,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5717,10 +5722,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45547</v>
+        <v>45343</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5733,7 +5738,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5776,7 +5781,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5790,10 +5795,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45317</v>
+        <v>45971</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5806,7 +5811,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5849,7 +5854,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5863,10 +5868,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45392</v>
+        <v>45092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5879,7 +5884,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5922,7 +5927,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5936,10 +5941,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45392</v>
+        <v>45628</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5952,7 +5957,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5995,7 +6000,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6009,10 +6014,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45318</v>
+        <v>45755</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6025,7 +6030,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6068,7 +6073,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6082,10 +6087,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45318</v>
+        <v>44657</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6097,8 +6102,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6141,7 +6151,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6155,10 +6165,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45061</v>
+        <v>45426</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6170,8 +6180,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6214,7 +6229,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6228,10 +6243,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44876</v>
+        <v>45993</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6243,8 +6258,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6287,7 +6307,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6301,10 +6321,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45555</v>
+        <v>44923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6317,7 +6337,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6360,7 +6380,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6374,10 +6394,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45429</v>
+        <v>44720</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6390,7 +6410,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6433,7 +6453,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6447,10 +6467,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45498</v>
+        <v>46006</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6462,13 +6482,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6511,7 +6526,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6525,10 +6540,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44903</v>
+        <v>45875</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6541,7 +6556,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6584,7 +6599,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6598,10 +6613,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45569</v>
+        <v>45273</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6614,7 +6629,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6657,7 +6672,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6671,10 +6686,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45392</v>
+        <v>45318</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6687,7 +6702,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6730,7 +6745,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6744,10 +6759,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44657</v>
+        <v>45399</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6759,13 +6774,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6808,7 +6818,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6822,10 +6832,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45348</v>
+        <v>45397</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6838,7 +6848,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.9</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6881,7 +6891,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6895,10 +6905,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45043</v>
+        <v>45162</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6911,7 +6921,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6954,7 +6964,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6968,10 +6978,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45318</v>
+        <v>45343</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6983,8 +6993,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>10.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7027,7 +7042,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7041,10 +7056,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45162</v>
+        <v>45320</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7057,7 +7072,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7100,7 +7115,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7114,10 +7129,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44720</v>
+        <v>45652</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7130,7 +7145,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7173,7 +7188,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7187,10 +7202,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45755</v>
+        <v>45318</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7203,7 +7218,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7246,7 +7261,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7256,14 +7271,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45532</v>
+        <v>45628</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7276,7 +7291,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7319,7 +7334,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7333,10 +7348,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45320</v>
+        <v>44903</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7349,7 +7364,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7392,7 +7407,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7406,10 +7421,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44923</v>
+        <v>44922</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7421,8 +7436,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7465,7 +7485,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7479,10 +7499,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45434</v>
+        <v>46035</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7495,7 +7515,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7538,7 +7558,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35899-2026</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7552,10 +7572,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46266</v>
+        <v>46125</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7568,7 +7588,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7611,7 +7631,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7625,10 +7645,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45334</v>
+        <v>44876</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7641,7 +7661,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7684,7 +7704,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7698,10 +7718,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45329</v>
+        <v>45434</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7713,13 +7733,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7762,7 +7777,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7776,10 +7791,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45330</v>
+        <v>45320</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7791,13 +7806,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>18.4</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7840,7 +7850,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7854,10 +7864,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45089</v>
+        <v>44943</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7870,7 +7880,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7913,7 +7923,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7927,10 +7937,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45426</v>
+        <v>45572</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7942,13 +7952,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +7996,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8010,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45399</v>
+        <v>44827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8026,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8069,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8083,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45755</v>
+        <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8099,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>14</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8142,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8156,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45092</v>
+        <v>45180</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8172,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8215,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8229,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45318</v>
+        <v>45769</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8245,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8288,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8297,10 +8302,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45162</v>
+        <v>45112</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8312,8 +8317,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8366,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8366,14 +8376,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45628</v>
+        <v>45838</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8396,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8439,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8453,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45628</v>
+        <v>45392</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8459,7 +8469,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.5</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8502,7 +8512,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8516,10 +8526,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45204</v>
+        <v>45600</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8529,11 +8539,6 @@
       <c r="G98" t="inlineStr">
         <is>
           <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -8580,7 +8585,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 35899-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8594,10 +8599,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45728</v>
+        <v>46266</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8609,13 +8614,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 951-2024</t>
+          <t>A 31291-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45301</v>
+        <v>46218</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1419,16 +1419,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>28.1</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1458,149 +1453,154 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Sandödla
+Hasselmus</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 951-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bredbrämad bastardsvärmare
 Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31291-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Sandödla
-Hasselmus</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45343</v>
+        <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1741,16 +1741,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>22.7</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1759,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1771,10 +1766,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1783,46 +1778,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1836,10 +1831,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45318</v>
+        <v>45407</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1852,16 +1847,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1876,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1888,46 +1883,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1936,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45434</v>
+        <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1957,20 +1952,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1981,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1997,42 +1992,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45600</v>
+        <v>46114</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2062,7 +2057,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2095,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2106,38 +2101,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46183</v>
+        <v>46114</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,10 +2162,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2179,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2191,58 +2186,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44844</v>
+        <v>46125</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,10 +2267,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2284,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2296,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2312,42 +2307,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46114</v>
+        <v>45343</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2376,21 +2371,26 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>22.7</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -2401,58 +2401,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46114</v>
+        <v>45434</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2515,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2526,38 +2526,38 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46125</v>
+        <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2586,8 +2586,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>11.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2599,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2611,10 +2616,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2627,42 +2632,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2676,10 +2681,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>46183</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2691,16 +2696,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>11.4</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2737,42 +2737,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45407</v>
+        <v>45318</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2802,17 +2802,17 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>6.8</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2838,39 +2838,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45329</v>
+        <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,13 +3371,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3415,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3434,10 +3429,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3449,8 +3444,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45043</v>
+        <v>45318</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3566,7 +3566,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45317</v>
+        <v>44827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3639,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45204</v>
+        <v>45180</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3668,13 +3668,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3712,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3726,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45728</v>
+        <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3746,13 +3741,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3795,7 +3785,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3809,10 +3799,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45755</v>
+        <v>45324</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3824,8 +3814,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3868,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3882,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45547</v>
+        <v>45162</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3898,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3941,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3955,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45429</v>
+        <v>45652</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3971,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4014,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4028,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45392</v>
+        <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4044,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4087,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4101,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45392</v>
+        <v>45336</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4117,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4160,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4174,10 +4169,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45324</v>
+        <v>45397</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4189,13 +4184,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4238,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4252,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45336</v>
+        <v>45600</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4268,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4311,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4325,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45318</v>
+        <v>45273</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4341,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4384,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4398,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45318</v>
+        <v>44845</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4414,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4457,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4467,14 +4457,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45330</v>
+        <v>45700</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4486,13 +4476,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>18.4</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4535,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4549,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45555</v>
+        <v>45769</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4608,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4622,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45348</v>
+        <v>45875</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4638,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.9</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4681,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4695,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45532</v>
+        <v>45343</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4711,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4754,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4768,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45318</v>
+        <v>44943</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4784,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4827,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4841,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44978</v>
+        <v>45180</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4857,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4900,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4914,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45498</v>
+        <v>45343</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4935,7 +4920,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>10.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4978,7 +4963,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4992,10 +4977,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45089</v>
+        <v>45818</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5008,7 +4993,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5051,7 +5036,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5065,10 +5050,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45162</v>
+        <v>45320</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5081,7 +5066,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5124,7 +5109,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5138,10 +5123,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45180</v>
+        <v>45971</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5154,7 +5139,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5197,7 +5182,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5211,10 +5196,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45818</v>
+        <v>45547</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5227,7 +5212,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5270,7 +5255,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5284,10 +5269,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45061</v>
+        <v>45317</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5300,7 +5285,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5343,7 +5328,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5357,10 +5342,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45569</v>
+        <v>45993</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5372,8 +5357,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5416,7 +5406,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5430,10 +5420,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45334</v>
+        <v>45392</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5446,7 +5436,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5489,7 +5479,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5499,14 +5489,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45700</v>
+        <v>45392</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5519,7 +5509,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5562,7 +5552,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5576,10 +5566,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45162</v>
+        <v>45112</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5591,8 +5581,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5635,7 +5630,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5649,10 +5644,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45875</v>
+        <v>45838</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5665,7 +5660,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5708,7 +5703,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5722,10 +5717,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45343</v>
+        <v>45318</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5738,7 +5733,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5781,7 +5776,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5795,10 +5790,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45971</v>
+        <v>45318</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5811,7 +5806,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5854,7 +5849,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5868,10 +5863,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45092</v>
+        <v>45061</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5884,7 +5879,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5927,7 +5922,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5941,10 +5936,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45628</v>
+        <v>44876</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5957,7 +5952,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6000,7 +5995,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6014,10 +6009,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45755</v>
+        <v>45555</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6030,7 +6025,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6073,7 +6068,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6087,10 +6082,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44657</v>
+        <v>45429</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6102,13 +6097,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6151,7 +6141,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6165,10 +6155,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45426</v>
+        <v>46035</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6180,13 +6170,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6229,7 +6214,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6243,10 +6228,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45993</v>
+        <v>45498</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6264,7 +6249,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.8</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6307,7 +6292,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6321,10 +6306,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44923</v>
+        <v>44903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6337,7 +6322,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6380,7 +6365,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6394,10 +6379,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44720</v>
+        <v>45569</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6410,7 +6395,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6453,7 +6438,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6467,10 +6452,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46006</v>
+        <v>45392</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6483,7 +6468,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6526,7 +6511,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6540,10 +6525,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45875</v>
+        <v>44657</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6555,8 +6540,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6599,7 +6589,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6613,10 +6603,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45273</v>
+        <v>45348</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6629,7 +6619,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6672,7 +6662,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6686,10 +6676,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45318</v>
+        <v>45043</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6702,7 +6692,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6745,7 +6735,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6759,10 +6749,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45399</v>
+        <v>45875</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6775,7 +6765,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6818,7 +6808,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6832,10 +6822,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45397</v>
+        <v>46006</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6848,7 +6838,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6891,7 +6881,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6905,10 +6895,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45162</v>
+        <v>45318</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6921,7 +6911,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6964,7 +6954,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6978,10 +6968,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45343</v>
+        <v>45162</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6993,13 +6983,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>10.6</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7042,7 +7027,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7056,10 +7041,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45320</v>
+        <v>44720</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7072,7 +7057,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7115,7 +7100,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7129,10 +7114,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45652</v>
+        <v>45755</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7145,7 +7130,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7188,7 +7173,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7202,10 +7187,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45318</v>
+        <v>46125</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7218,7 +7203,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7261,7 +7246,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7271,14 +7256,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45628</v>
+        <v>45532</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7291,7 +7276,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7334,7 +7319,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7348,10 +7333,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44903</v>
+        <v>45320</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7364,7 +7349,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7407,7 +7392,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7421,10 +7406,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44922</v>
+        <v>44923</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7436,13 +7421,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7485,7 +7465,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7499,10 +7479,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46035</v>
+        <v>45434</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7515,7 +7495,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7558,7 +7538,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7572,10 +7552,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46125</v>
+        <v>45334</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7588,7 +7568,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7631,7 +7611,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7645,10 +7625,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44876</v>
+        <v>45329</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7660,8 +7640,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7704,7 +7689,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7718,10 +7703,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45434</v>
+        <v>45330</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7733,8 +7718,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>18.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7777,7 +7767,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7791,10 +7781,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45320</v>
+        <v>45089</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7807,7 +7797,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7850,7 +7840,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7864,10 +7854,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44943</v>
+        <v>45426</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7879,8 +7869,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7923,7 +7918,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7937,10 +7932,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45572</v>
+        <v>45399</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7953,7 +7948,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7996,7 +7991,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8010,10 +8005,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44827</v>
+        <v>45755</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8026,7 +8021,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8069,7 +8064,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8083,10 +8078,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44845</v>
+        <v>45092</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8099,7 +8094,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>14</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8142,7 +8137,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8156,10 +8151,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45180</v>
+        <v>45318</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8172,7 +8167,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8215,7 +8210,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8229,10 +8224,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45769</v>
+        <v>45162</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8245,7 +8240,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8288,7 +8283,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8298,14 +8293,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45112</v>
+        <v>45628</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8317,13 +8312,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8366,7 +8356,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8380,10 +8370,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45838</v>
+        <v>45628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8396,7 +8386,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8439,7 +8429,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8453,10 +8443,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45392</v>
+        <v>45204</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8468,8 +8458,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8512,7 +8507,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8526,10 +8521,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45600</v>
+        <v>45728</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8541,8 +8536,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8602,7 +8602,7 @@
         <v>46266</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 31291-2026</t>
+          <t>A 951-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46218</v>
+        <v>45301</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1419,11 +1419,16 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>28.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1453,154 +1458,149 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare
+Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31291-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIMRISHAMN</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sandödla
 Hasselmus</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 31291-2026 artfynd.xlsx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 31291-2026 karta.png", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 31291-2026 georefererad karta.tif", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 31291-2026 FSC-klagomål.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 31291-2026 FSC-klagomål mail.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 31291-2026 tillsynsbegäran.docx", "A 31291-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 31291-2026 tillsynsbegäran mail.docx", "A 31291-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 951-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SIMRISHAMN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Bredbrämad bastardsvärmare
-Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 951-2024 artfynd.xlsx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 951-2024 karta.png", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 951-2024 georefererad karta.tif", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 951-2024 FSC-klagomål.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 951-2024 FSC-klagomål mail.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 951-2024 tillsynsbegäran.docx", "A 951-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 951-2024 tillsynsbegäran mail.docx", "A 951-2024")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50134-2024</t>
+          <t>A 7082-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45600</v>
+        <v>45343</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1741,21 +1741,26 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>22.7</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -1766,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1778,46 +1783,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 16258-2024</t>
+          <t>A 22194-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1831,10 +1836,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45407</v>
+        <v>45069</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1846,8 +1851,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>11.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1859,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1871,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1887,42 +1897,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45802-2022</t>
+          <t>A 16258-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1936,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44844</v>
+        <v>45407</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1952,10 +1962,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1964,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1976,10 +1986,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1992,42 +2002,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Hartsticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 16258-2024 artfynd.xlsx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 16258-2024 karta.png", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 16258-2024 georefererad karta.tif", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 16258-2024 FSC-klagomål.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 16258-2024 FSC-klagomål mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 16258-2024 tillsynsbegäran.docx", "A 16258-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 16258-2024 tillsynsbegäran mail.docx", "A 16258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17038-2026</t>
+          <t>A 20090-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2051,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46114</v>
+        <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,7 +2067,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2090,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2101,38 +2111,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17022-2026</t>
+          <t>A 50134-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2156,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46114</v>
+        <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,7 +2172,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2195,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2206,38 +2216,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 50134-2024 artfynd.xlsx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 50134-2024 karta.png", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 50134-2024 georefererad karta.tif", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 50134-2024 FSC-klagomål.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 50134-2024 FSC-klagomål mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 50134-2024 tillsynsbegäran.docx", "A 50134-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 50134-2024 tillsynsbegäran mail.docx", "A 50134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18002-2026</t>
+          <t>A 3401-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46125</v>
+        <v>45318</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2267,17 +2277,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2291,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2303,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7082-2024</t>
+          <t>A 17038-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2356,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45343</v>
+        <v>46114</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2371,16 +2381,11 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>22.7</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2389,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2401,58 +2406,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 7082-2024 artfynd.xlsx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17038-2026 artfynd.xlsx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 7082-2024 karta.png", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17038-2026 karta.png", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 7082-2024 georefererad karta.tif", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17038-2026 georefererad karta.tif", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 7082-2024 FSC-klagomål.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17038-2026 FSC-klagomål.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 7082-2024 FSC-klagomål mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17038-2026 FSC-klagomål mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 7082-2024 tillsynsbegäran.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17038-2026 tillsynsbegäran.docx", "A 17038-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 7082-2024 tillsynsbegäran mail.docx", "A 7082-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17038-2026 tillsynsbegäran mail.docx", "A 17038-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20090-2024</t>
+          <t>A 17022-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45434</v>
+        <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2487,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2515,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2526,38 +2531,38 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 20090-2024 artfynd.xlsx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 17022-2026 artfynd.xlsx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 20090-2024 karta.png", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 17022-2026 karta.png", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 20090-2024 georefererad karta.tif", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 17022-2026 georefererad karta.tif", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 20090-2024 FSC-klagomål.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 17022-2026 FSC-klagomål.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 20090-2024 FSC-klagomål mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 17022-2026 FSC-klagomål mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 20090-2024 tillsynsbegäran.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 17022-2026 tillsynsbegäran.docx", "A 17022-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 20090-2024 tillsynsbegäran mail.docx", "A 20090-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 17022-2026 tillsynsbegäran mail.docx", "A 17022-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22194-2023</t>
+          <t>A 18002-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2571,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45069</v>
+        <v>46125</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2586,13 +2591,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>11.4</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2616,10 +2616,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2632,42 +2632,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 22194-2023 artfynd.xlsx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 18002-2026 artfynd.xlsx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 22194-2023 karta.png", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 18002-2026 karta.png", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 22194-2023 georefererad karta.tif", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 18002-2026 georefererad karta.tif", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 22194-2023 FSC-klagomål.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 18002-2026 FSC-klagomål.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 22194-2023 FSC-klagomål mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 18002-2026 FSC-klagomål mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 22194-2023 tillsynsbegäran.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 18002-2026 tillsynsbegäran.docx", "A 18002-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 22194-2023 tillsynsbegäran mail.docx", "A 22194-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 18002-2026 tillsynsbegäran mail.docx", "A 18002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26510-2026</t>
+          <t>A 45802-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46183</v>
+        <v>44844</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2737,42 +2737,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hartsticka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 45802-2022 artfynd.xlsx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 45802-2022 karta.png", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 45802-2022 georefererad karta.tif", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 45802-2022 FSC-klagomål.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 45802-2022 FSC-klagomål mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 45802-2022 tillsynsbegäran.docx", "A 45802-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 45802-2022 tillsynsbegäran mail.docx", "A 45802-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3401-2024</t>
+          <t>A 26510-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45318</v>
+        <v>46183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2811,10 +2811,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2838,39 +2838,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 3401-2024 artfynd.xlsx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/artfynd/A 26510-2026 artfynd.xlsx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 3401-2024 karta.png", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor/A 26510-2026 karta.png", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 3401-2024 georefererad karta.tif", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/kartor_geotiff/A 26510-2026 georefererad karta.tif", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 3401-2024 FSC-klagomål.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomål/A 26510-2026 FSC-klagomål.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 3401-2024 FSC-klagomål mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/klagomålsmail/A 26510-2026 FSC-klagomål mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 3401-2024 tillsynsbegäran.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsyn/A 26510-2026 tillsynsbegäran.docx", "A 26510-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 3401-2024 tillsynsbegäran mail.docx", "A 3401-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1291/tillsynsmail/A 26510-2026 tillsynsbegäran mail.docx", "A 26510-2026")</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43851-2024</t>
+          <t>A 5028-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45572</v>
+        <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,8 +3371,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3415,7 +3420,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62149-2022</t>
+          <t>A 42231-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3429,10 +3434,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>45180</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3444,13 +3449,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3405-2024</t>
+          <t>A 38846-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45318</v>
+        <v>45547</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3566,7 +3566,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42016-2022</t>
+          <t>A 19435-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44827</v>
+        <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3639,7 +3639,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42374-2023</t>
+          <t>A 14104-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45180</v>
+        <v>45392</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3712,7 +3712,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8721-2023</t>
+          <t>A 14106-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44978</v>
+        <v>45392</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3785,7 +3785,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4193-2024</t>
+          <t>A 17110-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45324</v>
+        <v>45755</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3814,13 +3814,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3858,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39221-2023</t>
+          <t>A 19141-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3872,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45162</v>
+        <v>45769</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3888,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3931,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61876-2024</t>
+          <t>A 6006-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3945,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45652</v>
+        <v>45336</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3961,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4004,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14000-2025</t>
+          <t>A 14103-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4018,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45740</v>
+        <v>45392</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4034,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4077,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6006-2024</t>
+          <t>A 3393-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4091,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45336</v>
+        <v>45318</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4107,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4150,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14702-2024</t>
+          <t>A 3395-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4164,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45397</v>
+        <v>45318</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4180,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4223,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50138-2024</t>
+          <t>A 4193-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4237,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45600</v>
+        <v>45324</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4257,8 +4252,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 63456-2023</t>
+          <t>A 50138-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45273</v>
+        <v>45600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45946-2022</t>
+          <t>A 5224-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44845</v>
+        <v>45330</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4403,8 +4403,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>14</v>
+        <v>18.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4452,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6830-2025</t>
+          <t>A 40584-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4457,14 +4462,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45700</v>
+        <v>45555</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4482,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4525,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19141-2025</t>
+          <t>A 8721-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4539,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45769</v>
+        <v>44978</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4555,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4598,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37189-2025</t>
+          <t>A 30911-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4612,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45875</v>
+        <v>45498</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4622,8 +4627,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4676,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7072-2024</t>
+          <t>A 7584-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4690,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45343</v>
+        <v>45348</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4706,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>6.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4749,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2554-2023</t>
+          <t>A 35692-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4763,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44943</v>
+        <v>45532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4779,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4822,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 42231-2023</t>
+          <t>A 3402-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4836,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45180</v>
+        <v>45318</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4852,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4895,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7083-2024</t>
+          <t>A 25475-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4909,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45343</v>
+        <v>45089</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4914,13 +4924,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>10.6</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4963,7 +4968,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28269-2025</t>
+          <t>A 47874-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4977,10 +4982,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45818</v>
+        <v>45204</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4992,8 +4997,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5036,7 +5046,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3602-2024</t>
+          <t>A 39238-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5050,10 +5060,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45320</v>
+        <v>45162</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5066,7 +5076,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5109,7 +5119,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55504-2025</t>
+          <t>A 42374-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5123,10 +5133,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45971</v>
+        <v>45180</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5139,7 +5149,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5182,7 +5192,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38846-2024</t>
+          <t>A 12000-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5196,10 +5206,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45547</v>
+        <v>45728</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5211,8 +5221,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5255,7 +5270,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3367-2024</t>
+          <t>A 20950-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5269,10 +5284,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45317</v>
+        <v>45061</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5285,7 +5300,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5328,7 +5343,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60059-2025</t>
+          <t>A 43724-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5342,10 +5357,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45993</v>
+        <v>45569</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5357,13 +5372,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5406,7 +5416,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14104-2024</t>
+          <t>A 5488-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5420,10 +5430,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45392</v>
+        <v>45334</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5436,7 +5446,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5479,7 +5489,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14106-2024</t>
+          <t>A 7072-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5493,10 +5503,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45392</v>
+        <v>45343</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5509,7 +5519,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5552,7 +5562,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30667-2023</t>
+          <t>A 39015-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5566,10 +5576,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45112</v>
+        <v>45162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5581,13 +5591,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5630,7 +5635,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32488-2025</t>
+          <t>A 26471-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5644,10 +5649,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45838</v>
+        <v>45092</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5660,7 +5665,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5703,7 +5708,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3393-2024</t>
+          <t>A 56764-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5717,10 +5722,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45318</v>
+        <v>45628</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5733,7 +5738,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5776,7 +5781,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3395-2024</t>
+          <t>A 17102-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5790,10 +5795,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45318</v>
+        <v>45755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5806,7 +5811,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5849,7 +5854,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20950-2023</t>
+          <t>A 14994-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5863,10 +5868,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45061</v>
+        <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5878,8 +5883,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5922,7 +5932,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53978-2022</t>
+          <t>A 18856-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5936,10 +5946,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44876</v>
+        <v>45426</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5951,8 +5961,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5995,7 +6010,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 40584-2024</t>
+          <t>A 62413-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6009,10 +6024,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45555</v>
+        <v>44923</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6025,7 +6040,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6068,7 +6083,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19435-2024</t>
+          <t>A 28269-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6082,10 +6097,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45429</v>
+        <v>45818</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6098,7 +6113,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>6.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6141,7 +6156,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1910-2026</t>
+          <t>A 23287-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6155,10 +6170,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46035</v>
+        <v>44720</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6171,7 +6186,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6214,7 +6229,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30911-2024</t>
+          <t>A 63456-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6228,10 +6243,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45498</v>
+        <v>45273</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6243,13 +6258,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6292,7 +6302,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58985-2022</t>
+          <t>A 55504-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6306,10 +6316,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44903</v>
+        <v>45971</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6322,7 +6332,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6365,7 +6375,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43724-2024</t>
+          <t>A 3404-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6379,10 +6389,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45569</v>
+        <v>45318</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6395,7 +6405,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6438,7 +6448,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14103-2024</t>
+          <t>A 6830-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6448,14 +6458,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45392</v>
+        <v>45700</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6468,7 +6478,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6511,7 +6521,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14994-2022</t>
+          <t>A 15039-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6525,10 +6535,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44657</v>
+        <v>45399</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6540,13 +6550,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6589,7 +6594,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7584-2024</t>
+          <t>A 37189-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6603,10 +6608,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45348</v>
+        <v>45875</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6619,7 +6624,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.9</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6662,7 +6667,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18682-2023</t>
+          <t>A 14702-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6676,10 +6681,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45043</v>
+        <v>45397</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6692,7 +6697,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6735,7 +6740,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37052-2025</t>
+          <t>A 14000-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6749,10 +6754,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45875</v>
+        <v>45740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6765,7 +6770,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6808,7 +6813,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 62316-2025</t>
+          <t>A 39221-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6822,10 +6827,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46006</v>
+        <v>45162</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6838,7 +6843,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6881,7 +6886,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3404-2024</t>
+          <t>A 7083-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6895,10 +6900,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45318</v>
+        <v>45343</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,8 +6915,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>10.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6954,7 +6964,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39238-2023</t>
+          <t>A 3602-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6968,10 +6978,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45162</v>
+        <v>45320</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6984,7 +6994,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7027,7 +7037,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23287-2022</t>
+          <t>A 18682-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7041,10 +7051,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44720</v>
+        <v>45043</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7057,7 +7067,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7100,7 +7110,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17102-2025</t>
+          <t>A 61876-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7114,10 +7124,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45755</v>
+        <v>45652</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7130,7 +7140,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7173,7 +7183,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18005-2026</t>
+          <t>A 3367-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7187,10 +7197,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46125</v>
+        <v>45317</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7203,7 +7213,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7246,7 +7256,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35692-2024</t>
+          <t>A 3405-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7260,10 +7270,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45532</v>
+        <v>45318</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7276,7 +7286,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7319,7 +7329,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3604-2024</t>
+          <t>A 56820-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7329,14 +7339,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45320</v>
+        <v>45628</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7349,7 +7359,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7392,7 +7402,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62413-2022</t>
+          <t>A 58985-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7406,10 +7416,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44923</v>
+        <v>44903</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7422,7 +7432,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7465,7 +7475,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20096-2024</t>
+          <t>A 62149-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7479,10 +7489,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45434</v>
+        <v>44922</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7494,8 +7504,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7538,7 +7553,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5488-2024</t>
+          <t>A 60059-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7552,10 +7567,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45334</v>
+        <v>45993</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7567,8 +7582,13 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7611,7 +7631,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5028-2024</t>
+          <t>A 30667-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7625,10 +7645,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45329</v>
+        <v>45112</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7646,7 +7666,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7689,7 +7709,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5224-2024</t>
+          <t>A 32488-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7703,10 +7723,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45330</v>
+        <v>45838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7718,13 +7738,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>18.4</v>
+        <v>4.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7767,7 +7782,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25475-2023</t>
+          <t>A 53978-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7781,10 +7796,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45089</v>
+        <v>44876</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7797,7 +7812,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7840,7 +7855,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18856-2024</t>
+          <t>A 20096-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7854,10 +7869,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45426</v>
+        <v>45434</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7869,13 +7884,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7918,7 +7928,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15039-2024</t>
+          <t>A 3604-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7932,10 +7942,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45399</v>
+        <v>45320</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7948,7 +7958,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7991,7 +8001,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17110-2025</t>
+          <t>A 2554-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8005,10 +8015,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45755</v>
+        <v>44943</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8021,7 +8031,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8064,7 +8074,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26471-2023</t>
+          <t>A 43851-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8078,10 +8088,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45092</v>
+        <v>45572</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8094,7 +8104,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8137,7 +8147,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3402-2024</t>
+          <t>A 42016-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,10 +8161,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45318</v>
+        <v>44827</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8167,7 +8177,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8210,7 +8220,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 39015-2023</t>
+          <t>A 45946-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8224,10 +8234,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45162</v>
+        <v>44845</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8240,7 +8250,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8283,7 +8293,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56820-2024</t>
+          <t>A 1910-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8293,14 +8303,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45628</v>
+        <v>46035</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8313,7 +8323,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8356,7 +8366,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56764-2024</t>
+          <t>A 62316-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8370,10 +8380,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45628</v>
+        <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8386,7 +8396,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8429,7 +8439,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 47874-2023</t>
+          <t>A 37052-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8443,10 +8453,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45204</v>
+        <v>45875</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8458,13 +8468,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8507,7 +8512,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12000-2025</t>
+          <t>A 18005-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8521,10 +8526,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45728</v>
+        <v>46125</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8536,13 +8541,8 @@
           <t>SIMRISHAMN</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8602,7 +8602,7 @@
         <v>46266</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45301</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46218</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>45343</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>45069</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>45407</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45318</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>46114</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>46125</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44844</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>46183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45180</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45547</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45392</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>45392</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45755</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45769</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45336</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45392</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>45318</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>45318</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45324</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45330</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45555</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>44978</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45498</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45348</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>45318</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45089</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>45204</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>45162</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45180</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45728</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>45061</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45569</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45334</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45343</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45092</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45628</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>45426</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44923</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45818</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>44720</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45273</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>45971</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>45318</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45700</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>45399</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>45875</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45397</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>45740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>45162</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45343</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45320</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>45043</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>45652</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>45317</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45318</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>45628</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>44903</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>44922</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>45993</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>45112</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>45838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44876</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>45434</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>45320</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44943</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>45572</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44827</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>44845</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>46035</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>45875</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>46125</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>46266</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46073</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIMRISHAMN.xlsx
+++ b/Översikt SIMRISHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45734</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45429</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>44687</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>44564</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45433</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45301</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46218</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44733</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>45343</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>45069</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>45407</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45318</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>46114</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>46125</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44844</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>46183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44953</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44606</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45180</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45547</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45392</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>45392</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45755</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45769</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45336</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45392</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>45318</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>45318</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45324</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45330</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45555</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>44978</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45498</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45348</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>45318</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45089</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>45204</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>45162</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45180</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45728</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>45061</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45569</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45334</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45343</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45092</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45628</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>45426</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44923</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45818</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>44720</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45273</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>45971</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>45318</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@